--- a/ciren_database/ciren_crash_summaries_categorized.xlsx
+++ b/ciren_database/ciren_crash_summaries_categorized.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,38 +473,14 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vehicle_encroachment</t>
+          <t>left_turn_straight</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>This crash case involves a seriously-injured, three-point-belt-restrained, 37-year-old, female driver of a 2017 Nissan Pathfinder, which was primarily involved in a near-side collision with the frontal plane of a 2017 Nissan Rogue.
-This two-vehicle collision occurred during daylight hours at the intersection of two urban trafficways. The north/south trafficway consists of two roadways divided by a raised concrete median. The southbound roadway consisted of two southbound through lanes with a right turn lane (three lanes). The one-way westbound channelized roadway consists of two travel lanes for through traffic and one dedicated right turn lane at the intersection. Both roadways are straight, with a speed limit of 72 km/h (45 mph), and the intersection is controlled by overhead, standard electric, tri-colored traffic signals. At the time of the crash, the weather was clear and the roadway surfaces were dry.
-Vehicle 1, a 2017 Nissan Pathfinder utility vehicle, was being driven by the 37-year-old female driver (CIREN case subject) in the number three, southbound, travel lane approaching the intersection from the north. The driver of V1 intended to cross through the intersection and continue traveling south.
-Vehicle 2, a 2017 Nissan Rogue compact utility vehicle, was traveling westbound in the far left lane, approaching the intersection from the east. The driver of V2 intended to cross through the intersection and continue traveling west.
-Both vehicles entered the intersection at the same time and the frontal plane of V2 struck the left side plane of V1 (Event 1). Vehicle 1 yawed in a counterclockwise direction and impacted a concrete curb (Event 2) with its right rear wheel. This impact caused V1 to trip and undergo a right-side-leading six quarter-turn rollover event (event 3). During the rollover event, V1 impacted a metal guardrail with its undercarriage (Event 4). Vehicle 1 came to rest on its top in the grassy area off the west edge of the roadway. Vehicle 1 was towed due to damage.
-Vehicle 2 rotated in a slight counterclockwise direction coming to rest off the west edge of the roadway. Vehicle 2 was towed due to disabling damage
-The driver, who was the only occupant of V1, was noted to be utilizing her three-point lap and shoulder belt (with retractor pretensioner actuated), and the vehicle was equipped with advanced frontal airbags, seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. As a result of the first impact, the driver's curtain and backrest-mounted hip/torso airbags deployed. The frontal airbags deployed 36 msec later into the collision sequence. The drivers of both vehicles sustained injuries and were transported by land to a local trauma center for treatment. The driver of V2 was treated and released. The driver of V1 was admitted with serious injuries and enrolled as the CIREN case occupant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>42</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>left_turn_straight</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
         <is>
           <t>This crash case involves a seriously-injured, belt-restrained, 48-year-old, female driver of a 2007 Dodge Nitro compact utility vehicle, which was primarily involved in a frontal collision with the frontal plane of a 2005 Dodge Grand Caravan Minivan.
 This two-vehicle collision occurred during evening hours on a dark, unlit, asphalt, county roadway. The north/south roadway consists of two lanes with a single travel lane in each travel direction without traffic controls. The roadway is straight, with a posted speed limit of 72 km/h (45 mph). At the time of the crash, the weather was clear and the roadway surface was dry.
@@ -515,19 +491,19 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
         <v>56</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>vehicle_encroachment</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>This investigation focused on the injury mechanisms of a belted, 53-year-old, female driver with a deployed frontal airbag. She sustained serious injuries when the compact utility vehicle she was driving (V1) was involved in a frontal, right-angle crash to a large pickup truck (V2). No other passengers were in the vehicle.
 The crash occurred during early evening hours on a dark but lighted, wet road under cloudy skies. The roadway consisted of an intersection between a suburban connector road and a neighborhood. There was a two-way, two-lane, east/west suburban road with a posted speed limit of 72 km/h (45 mph) joined with a two-way, two-lane, north/south neighborhood road controlled with stop signs. For V1’s westbound approach, the bituminous road was curved left with 4% superelevation and on a 1.5% downhill grade. For V2’s northbound approach, the road was straight and on a 4% uphill grade.
@@ -537,19 +513,19 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
         <v>58</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>left_turn_straight</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>This crash case involves a seriously-injured, belt-restrained, 70-year-old, female front right passenger of a 2017 Nissan Rogue compact utility vehicle. The Nissan Rogue (case vehicle) was primarily involved in a frontal collision with the right plane of a 2009 Lexus ES-350 four-door sedan.
 This two-vehicle collision occurred during the early evening hours (dark, street lights present) at the intersection of two urban roadways. The straight and level north/south roadway consists of three northbound lanes and four southbound lanes. The northbound lanes are composed of two straight through lanes and one left turn lane. The southbound lanes are composed of one right turn lane, two straight through lanes, and one left turn lane. The roadways are straight and has a 3% uphill grade for the northbound lane and a 3% downhill grade for the southbound lanes leading into the intersection. The speed limit for the north/south roadway is 72 kmph (45 mph), and the intersection is controlled by overhead, standard electric, tri-colored traffic signals. At the time of the crash, the weather was clear and the asphalt roadway surfaces were dry.
@@ -561,19 +537,19 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
         <v>63</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>lane_departure_opposite</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>This crash case involves a seriously-injured, belt-restrained, 46-year-old female driver of a 2012 Toyota Camry four-door sedan, which was primarily involved in a frontal impact collision with a 2002 BMW X5 compact utility vehicle.
 This two-vehicle collision occurred during daylight hours on a two-way asphalt roadway with one northbound travel lane and one southbound travel lane. The roadway is straight, with a posted speed limit of 72 km/h (45 mph), and without traffic controls. At the time of the crash, the weather was cloudy and the roadway surface was wet.
@@ -584,6 +560,20 @@
 The drivers of both vehicles sustained injuries and were transported by land to a local trauma center for treatment. The driver of V1 was admitted with serious injuries and enrolled as the CIREN case occupant. The passenger of V1 sustained injuries and was transported to the local trauma center where she was admitted.</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>67</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>vehicle_encroachment</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -658,6 +648,1043 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>left_turn_straight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 62-year-old, male driver with deployed frontal steering wheel-mounted and roof rail-mounted curtain airbags. The driver sustained serious injuries when his compact utility vehicle was involved in a frontal impact with a large utility. No other passengers were in the vehicle.
+The crash occurred during daylight hours on a dry, bituminous, north/south roadway under clear skies within the confines of a four-legged intersection. The northbound and southbound travel lanes were separated by a raised traffic island. The north trafficway consisted of four bituminous travel lanes (two straight lanes, one left turn and one right turn) with a posted speed limit of 72 km/h (45 mph) and a -2.1% grade at the point of impact. The south trafficway consisted of four bituminous travel lanes (two straight lanes, one left turn and one right turn) with a posted speed limit of 72 km/h (45 mph). The north/south trafficway is intersected by an entrance/exit to a townhouse community on the west and an entrance/exit ramp to a county highway on the east side. This intersection is controlled by standard tri-colored traffic signals for each direction.
+A 2016 Volkswagen Tiguan (V1) was traveling north in the left through lane. A 2017 Honda Pilot (V2) was traveling south in the left turn lane.
+As V2 entered the intersection in an attempt to execute a left turn in front of V1, it was impacted on the front-right by the front plane of V1 (Event #1). After initial impact, V1 rotated in a clockwise direction impacting its left side with the back of V2 before traveling to final rest partially on a raised traffic island in the northeast quadrant of the intersection. After initial impact, V2 rotated counter-clockwise before impacting its back plane with the left side of V1 (Event #2). V2 traveled to its final resting position in the northeast quadrant of the intersection. V1 and V2 were towed from the scene due to damage.
+The 62-year-old male driver of V1 (case occupant) was presumed to be seated in an upright position at the time of the impact with V2 (Event #1). The driver was belted at the time of the crash as evidenced by loading marks and confirmed by EDR data. The frontal steering wheel-mounted and roof rail-mounted curtain airbags deployed upon impact with V2. This case occupant was transported by ground from the scene to a local trauma center for treatment of serious injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>136</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of an unbelted 26-year-old female driver (case occupant) of a 2014 Toyota Camry LE four-door sedan (Vehicle 1), which was primarily involved in a moderate, one-o’clock far-side impact by the frontal plane of a 2008 Nissan Altima two-door coupe (Vehicle 2). Vehicle 1 was noted to be equipped with frontal and knee bolster airbags (driver and front right passenger positions), seat backrest-mounted side airbags (first and second row outboard seating positions) and curtain airbags (first and second row outboard seating positions).
+This crash occurred during the pre-midnight hour (dark, street lights present), of an early spring weekend day, at the intersection of a north/south roadway and a one-way, westbound roadway. The north/south roadway consisted of three northbound travel lanes and two southbound travel lanes. This roadway was straight with a downhill grade for the northbound travel direction. The westbound roadway intersected the north/south roadway on the east and west sides. The western leg of this roadway was offset from the eastern leg and intersected the north/south roadway at an obtuse angle (as one travels northbound). The intersection was controlled by overhead, standard electric, tri-colored traffic signals. At the time of the crash, the weather was clear and the bituminous roadway surfaces were dry. The north/south roadway had a posted speed limit of 25 mph (40 kmph) for both travel directions. The overall environment was urban.
+The driver, and sole occupant, of Vehicle 1 was traveling northbound in the far left northbound travel lane. Just prior to the crash, the driver of Vehicle 1 slowed to a stop, of short time duration, before accelerating and initiating a left turn. The driver of Vehicle 1 intended to turn left at the intersection and continue traveling westbound.
+The driver, and sole occupant, of Vehicle 2 was traveling in the right southbound travel lane approaching the intersection from the north. The driver of Vehicle 2 intended to pass through the intersection and continue traveling south.
+Both vehicles entered the intersection at the same time and the frontal plane of Vehicle 2 struck the right-side plane (right front) of Vehicle 1 (Event 1). As a result of this impact, Vehicle 1 rotated counterclockwise as Vehicle 2 rotated slightly clockwise. Both vehicles subsequently “side-slapped” with the right-side plane (right rear) of Vehicle 1 striking the left-side plane (left rear) of Vehicle 2 (Event 2). Both vehicles were re-directed towards the southwest sector of the intersection and came to rest facing southwest. As a result of the first impact (Event 1), the driver’s frontal and knee bolster airbags deployed as did both side rail curtain airbags, and the right front and rear seat backrest-mounted side airbags.
+Following the collision, the unbelted 26-year-old female driver of Vehicle 1 (case occupant) refused medical treatment at the scene. However, the case occupant sought medical treatment the following day at a local hospital, but was transferred, via ground unit, to a nearby trauma center and hospitalized with minor to moderate injuries. The driver of Vehicle 2 was reported to have been transported directly to a local hospital by a relative; however, the extent of her injuries and treatment, if any, are unknown. Both vehicles were towed from the scene due to damage sustained in the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>145</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>car_following</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 46-year-old, male front right seat passenger with deployed frontal, knee bolster and side curtain airbags. He sustained serious injuries when the subcompact vehicle he was traveling in impacted the rear plane of a large utility vehicle. The only other occupant in the vehicle at the time of the crash was a belted, 15-year-old, female driver with deployed frontal, knee bolster and side curtain airbags.
+The crash occurred during the afternoon hours on a dry road under clear skies (sunny). The trafficway consisted of two eastbound travel lanes (with a shoulder) and two westbound travel lanes, divided by a center grassy median. Both directions had a posted speed limit of 97 km/h (60 mph). For V1 and V2’s eastbound approach, the bituminous road was straight with a -3.9% superelevation on a +2.5% grade.
+A 2013 Chevrolet Spark (V1) was traveling east in the left lane approaching a line of traffic. A 2002 Chevrolet Suburban (V2) was also traveling east in the left lane in front of V1.
+As V1 was traveling in the left travel lane, the driver saw a non-contact vehicle immediately in front of her abruptly steer into the right lane in an attempt to avoid impacting a stopped vehicle. V1 attempted to brake and steer to the left but was unable to avoid impacting the rear of V2 with its front (Event 1). After initial impact V1 traveled around V2 (left side) and into the right travel lane. It then traveled around a line of stopped vehicles, and then back to the left lane before traveling off into the north median. As V1 traveled off the roadway, it impacted a small sign with its left side before traveling to final rest (Event 2). V2 was stopped in a line of traffic when it was impacted in the rear by the front of V1. After initial impact, V2 was pushed slightly forward to it's final resting position in the eastbound lane facing east. V1 was towed from the scene. V2 was not towed from the scene and no injuries were reported.
+The 46-year-old male front right passenger in V1 was presumed to be seated in an upright position. He was belted at the time of the crash as evidenced by loading marks on the seat belt webbing. The pretensioner was also reported as actuated by the event data recorder. At the case occupant’s seating position there were several air bags available including frontal, knee bolster, seat back and a side curtain airbag. The frontal, knee bolster and side curtain air bags all deployed as a result of the frontal crash. This occupant was airlifted to a local trauma center for treatment of his serious injuries. The 15-year-old female driver of V1 was transferred by ambulance to a local hospital where she was treated and released with only minor injuries sustained in the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>162</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 43-year-old, male driver with deployed front and side airbags. He sustained moderate injuries when the compact utility vehicle he was driving was involved in a multi-event crash to a large pickup truck and several roadside features. No other passengers were in the vehicle.
+The crash occurred during morning daylight hours on a dry road under clear skies. The roadway consisted of a two-way, two-lane, northeast/southwest rural highway with a posted speed limit of 72 km/h (45 mph). The bituminous road was straight in V1’s southwestern direction of travel on a one percent uphill grade. V2 approached from a right curve with seven percent superelevation that transitioned into a straight section of road with a two percent uphill grade. There were no traffic controls in the area of interest.
+A 2016 Toyota 4-Runner compact utility (V1) was traveling southwest in the right lane. A 2000 Dodge Dakota large pickup truck (V2) was traveling northeast when it crossed left across the centerline of the two-lane road. V1 braked and steered right in avoidance.
+The front left corner of V1 struck the front left corner of V2 in a small overlap configuration (Event 1). The moment arm of the impact caused V1 to rotate rapidly counterclockwise, leading it to depart the right side of the road and strike a mailbox with wooden post (Event 2) followed by a bush approximately one meter in height (Event 3) with its right plane. V1’s remaining momentum carried it approximately 20 meters from initial impact, bringing it to rest on the northwest roadside facing opposite its initial direction of travel. V2 also traveled off the northwest side of the road after the Event 1 impact, striking a large bush with its front plane (Event 4) before coming to rest on the roadside. Both vehicles were towed due to damage.
+The 43-year-old male driver was presumed to be seated in an upright position. He was belted at the time of the crash as evidenced by abrasion to the shoulder belt webbing with indeterminate payout, as well as loading of the latch plate. The available retractor pretensioner was actuated and found in the extended and locked (used) position at inspection. The vehicle was not equipped with anchor or buckle pretensioners. The steering wheel hub, left knee bolster, both roof side rail, and both seat back airbags deployed upon the initial impact. The available right instrument panel and right knee bolster airbags did not deploy for the unoccupied right front seating position. No other airbags were installed. This occupant was transported to a trauma center for treatment of moderate injuries.
+The 37-year old, female driver of V2 was also transported to a trauma center for treatment of police-reported non-incapacitating injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>180</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>left_turn_straight</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 23-year-old, female driver with deployed frontal steering wheel-mounted, knee-mounted, seat back-mounted torso/pelvis, and roof rail-mounted curtain airbags. The driver sustained serious injuries when her subcompact vehicle was involved in a full-frontal impact (head-on) with a compact utility vehicle. This investigation also focuses on the injury mechanisms of a belted, 22-year-old, pregnant (second trimester) female front right passenger with deployed frontal top-mounted instrument panel and roof rail-mounted curtain airbags, who sustained severe injuries. No other passengers were in the vehicle.
+The crash occurred during the evening hours on a dry, bituminous two-lane roadway under clear skies. There is one westbound travel lane and one eastbound travel lane with a posted speed limit of 89 km/h (55 mph). The westbound travel lane has a pre-crash grade of +1.8%. The eastbound travel lane has a pre-crash grade of -1.8%. The lanes were divided by a double yellow line and there are no traffic control devices. The crash occurred just west of a four-leg intersection with a north/south two-lane road. The north/south traffic was controlled by stop signs.
+The CIREN case vehicle was a 2012 Ford Fiesta (V1) traveling west. A 1997 Honda Passport (V2) was traveling east and was being pursued by a police car. Vehicle 2 crossed over into the west travel lane in an attempt to execute a left turn (as it approached the intersection). As V1 was exiting the mouth of the intersection, it was impacted on the front plane by the front plane of V2 (event #1). The Principal Direction of Force (PDOF) relative to V1 was 350 degrees with a longitudinal delta-V of -75.9 km/h (-47.2 mph) recorded by the EDR. The force of the impact caused V1 to rotate clockwise and V2 to rotate counterclockwise. The left plane of V1 struck the right plane of V2 in a secondary side-slap (event #2). Vehicle 1 continued in a northeast direction before traveling to its final rest position in the northwest quadrant of the intersection facing northeast (partially off the road). Vehicle 2 continued to rotate counterclockwise to its final resting position off the west road edge (just west of the intersection) facing west. Vehicle 1 and V2 were towed from the scene due to damage.
+The 23-year-old female driver (case occupant #1) was presumed to be seated in an upright position at the time of the impact with V2. The driver was belted at the time of the crash as evidenced by loading marks and confirmed by EDR data. The frontal steering wheel mounted airbag , knee airbag, seat back-mounted torso/pelvis airbag, and roof rail-mounted curtain airbag all deployed upon impact (event #1) with V2. This case occupant was transported by ground from the scene to a local hospital and then later transferred by air to a trauma center for treatment of serious injuries.
+The 22-year-old female passenger (case occupant #2) was presumed to be seated in an upright position at the time of the impact with V2. She was belted at the time of the crash as evidenced by loading marks and confirmed by EDR data. The frontal IP-mounted airbag and roof rail-mounted curtain airbag deployed upon impact (event #1) with V2. This case occupant was transported by ground from the scene to a trauma center for treatment of severe injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>220</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>left_turn_straight</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>This crash case involved a seriously injured, belted 53-year-old male driver (case subject) of a 2018 Ford Fiesta four-door sedan, which was primarily involved in a frontal collision with a 2002 Ford Ranger pickup. There was also a seriously injured, unbelted, 52-year-old female right-front passenger (case subject) in the 2018 Ford Fiesta.
+This two-vehicle collision occurred during the night hours (dark, lit) in the intersection of two roadways. The southern leg of the intersection consisted of two northbound lanes and two-southbound lanes that were separated by a concrete island. The northern leg of the intersection consisted of two lanes, one for northbound travel and one for southbound travel. All travel lanes were level and the roadways were wet due to rain. The posted speed limit for the north/south roadway was 64 kmph (40 mph).
+Vehicle 1, the 2018 Ford Fiesta four-door sedan, was being driven by the 53-year-old male driver (CIREN case subject) in the far-right, northbound travel lane, attempting to cross over the intersection and continue heading north. Vehicle 1 was also occupied by a 52-year-old female right-front passenger (CIREN case subject). Vehicle 2, the 2002 Ford Ranger pickup, was traveling southbound, attempting to turn left to onto the eastbound roadway.
+As Vehicle 1 entered the intersection, its front plane was contacted by the frontal plane of Vehicle 2 (Event 1). This impact caused Vehicle 1 to rotate clockwise and Vehicle 2 to rotate counterclockwise, resulting in the right plane of Vehicle 2 striking the left plane of Vehicle 1 (Event 2). Both vehicles came to rest in the intersection facing in an easterly direction. Both vehicles sustained disabling damage and were towed from the crash scene.
+The driver was noted as utilizing his three-point lap and shoulder belt (with retractor pretensioner), and the vehicle was equipped with advanced frontal airbags, seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. The passenger was noted as not utilizing her three-point lap and shoulder belt. Because of the impact, the driver and passenger's frontal airbags deployed. The driver's seatback-mounted airbag along with the driver's and passenger’s roof rail airbags deployed. Both the driver and passenger of Vehicle 1 sustained serious injuries and were transported by land to a local medical facility center for treatment. The injury status of the occupant in Vehicle 2 was unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>221</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>left_turn_straight</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>This crash case involved a seriously injured, belted 53-year-old male driver (case subject) of a 2018 Ford Fiesta four-door sedan, which was primarily involved in a frontal collision with a 2002 Ford Ranger pickup. There was also a seriously injured, unbelted, 52-year-old female right-front passenger (case subject) in the 2018 Ford Fiesta.
+This two-vehicle collision occurred during the night hours (dark, lit) in the intersection of two roadways. The southern leg of the intersection consisted of two northbound lanes and two-southbound lanes that were separated by a concrete island. The northern leg of the intersection consisted of two lanes, one for northbound travel and one for southbound travel. All travel lanes were level and the roadways were wet due to rain. The posted speed limit for the north/south roadway was 64 kmph (40 mph).
+Vehicle 1, the 2018 Ford Fiesta four-door sedan, was being driven by the 53-year-old male driver (CIREN case subject) in the far-right, northbound travel lane, attempting to cross over the intersection and continue heading north. Vehicle 1 was also occupied by a 52-year-old female right-front passenger (CIREN case subject). Vehicle 2, the 2002 Ford Ranger pickup, was traveling southbound, attempting to turn left to onto the eastbound roadway.
+As Vehicle 1 entered the intersection, its front plane was contacted by the frontal plane of Vehicle 2 (Event 1). This impact caused Vehicle 1 to rotate clockwise and Vehicle 2 to rotate counterclockwise, resulting in the right plane of Vehicle 2 striking the left plane of Vehicle 1 (Event 2). Both vehicles came to rest in the intersection facing in an easterly direction. Both vehicles sustained disabling damage and were towed from the crash scene.
+The driver was noted as utilizing his three-point lap and shoulder belt (with retractor pretensioner), and the vehicle was equipped with advanced frontal airbags, seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. The passenger was noted as not utilizing her three-point lap and shoulder belt. Because of the impact, the driver and passenger's frontal airbags deployed. The driver's seatback-mounted airbag along with the driver's and passenger’s roof rail airbags deployed. Both the driver and passenger of Vehicle 1 sustained serious injuries and were transported by land to a local medical facility center for treatment. The injury status of the occupant in Vehicle 2 was unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>226</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cut_in</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>This crash involved an impact between the right front plane of a 2017 Nissan Sentra four-door sedan and the left plane of a 2015 Chevrolet Cruze four-door sedan. There was also a subsequent impact between the front plane of the Nissan and a brick wall. The severely injured, unbelted, 69-year-old female right-front passenger (CIREN case subject) and seriously injured, unbelted, 59-year-old female right-rear passenger (CIREN case subject) of the Nissan were both CIREN case subjects.
+This two-vehicle crash occurred during the late-morning hours of a fall weekend on a rural three-lane roadway. The one-way north roadway was composed of three straight northbound lanes with a negative grade. The weather was cloudy and the asphalt roadway was dry with a speed limit of 48 kmph (30 mph). The northbound roadway had no traffic controls.
+Vehicle 1, a 2017 Nissan Sentra four-door sedan, was being driven by a 61-year-old female driver in the far left northbound travel lane, intending to continue heading north. Vehicle 2, a 2015 Chevrolet Cruze four-door sedan, was traveling in the center northbound travel lane with the intent of continuing north. The driver of Vehicle 2 steered left in an attempt to change lanes to the left. This maneuver caused the left rear of Vehicle 2 to strike the right front of Vehicle 1 (Event 1). The driver of Vehicle 1 steered left in an attempt to avoid a collision, which caused Vehicle 1 to depart the roadway to the left. Vehicle 1 then crossed an intersecting roadway before it struck a brick wall of a building with its frontal plane (Event 2). Vehicle 1 came to rest at impact, facing a northwesterly direction while partially off the roadway and partially in the adjacent roadway. Vehicle 2 was driven onto the left shoulder of the roadway and came to rest north of the intersecting roadway, facing a northerly direction. Vehicle 1 was towed after sustaining disabling damage. Vehicle 2 was driven from the scene.
+The driver of Vehicle 1 was noted as utilizing her three-point lap and shoulder belt (with retractor pretensioner), and the vehicle was equipped with advanced frontal airbags, seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. During the first impact, the driver's frontal, passenger's frontal, passenger's side seat backrest-mounted, and right roof rail-mounted airbags deployed. No additional airbags deployed. The driver of Vehicle 1 sustained non-incapacitating injuries and was transported by land to a local medical facility center for treatment. The right-front passenger (CIREN case subject) and right-rear passenger (CIREN case subject) of Vehicle 1 were both transported to a regional trauma center where they received treatment for their injuries. The driver of Vehicle 2 did not sustain injury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>227</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>vehicle_encroachment</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted 50-year-old female driver with a deployed frontal steering wheel-mounted airbag and roof rail-mounted curtain airbags. The driver sustained moderate injuries when the four-door large utility vehicle she was in was involved in a T-bone type impact (frontal) with the right side of a compact four-door pickup. The compact four-door pickup also impacted a parked intermediate sedan (not-in-transport vehicle).
+This two-vehicle collision occurred during the daylight hours at the intersection of two roadways. The north/south roadway consists of four northbound lanes (two through lanes and a dedicated left and right turn lane) and four southbound lanes (two through lanes and a dedicated left and right turn lane). The north travel lanes are bituminous with a +0.4 percent grade and the south travel lanes are bituminous with a +1 percent grade. These roadways are separated by a grassy median and have a posted speed limit of 97 km/h (60 mph). The north/south roadways are intersected by three west/east lanes (one through lane and one right turn lane for west and one east lane). The west/east lanes are separated by a double yellow line and have a posted speed limit of 72 km/h (45 mph). At the median crossover, there is a stop sign and stop bar for each direction. In the east direction there is a +0.5 percent grade. All roadways are straight and the intersection is controlled by stop signs for west and east travel only. At the time of the crash, the weather was cloudy and the roadway surface was dry.
+Vehicle 1, 2015 Chevrolet Traverse four-door large utility vehicle, was being driven by the 50-year-old female driver (CIREN case subject) traveling north in the left through lane. The driver of V1 entered the intersection intending to continue traveling north.
+Vehicle 2, a 2017 Toyota Tacoma compact four-door pickup, was in the median crossover facing east. The driver of V2 intended to cross through the intersection and continue traveling east.
+Both vehicles entered the intersection at the same time and the frontal-plane of V1 impacted the right side of V2 (Event 1). After initial impact, V1 rotated 20 degrees clockwise impacting its left side with the right side of V2 (Event 2/side slap). Vehicle 1 continued traveling off the northeast quadrant of the intersection and entered a gas station lot. After rotating 180 degrees and beginning to travel backwards, V1 sideswiped a safety pole (Event 3) used to protect the gas pumps from being contacted. This was V1’s final resting position (against the pole facing south).
+After initial impact, V2 rotated counter-clockwise 80 degrees impacting its right side with the left side of V2 (Event 2). Vehicle 2 continued on in a northeasterly direction traveling off the roadway and entered the same gas station lot as V1. Vehicle 2 impacted a parked vehicle with its front left (Event 4) and then impacted and dislodged a gas pump (Event 5) with its front bumper. Finally, V2 impacted a steel overhang support with its right side just before final rest (Event 6). Both vehicles were towed from the scene due to damage sustained in the crash. The parked vehicle had minor damage and was driven from the scene.
+The 50-year-old, female driver (case occupant 1) was presumed to be seated in an upright position at the time of the impact with V2. This occupant was belted at the time of the crash as evidenced by the EDR and corresponding soft tissue injuries. The frontal steering wheel-mounted airbag and roof rail-mounted curtain airbag deployed upon impact (Event 1) with V2. This case occupant was transported by ambulance from the scene to a local trauma center for treatment of moderate injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>244</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously injured, belt-restrained, 21-year-old female driver of a 2013 Scion tC three-door hatchback, which was primarily involved in a far-side collision with the front of a 2010 Ford Focus four-door sedan.
+This two-vehicle collision occurred during the mid-afternoon hours on a winter weekday at the intersection of two suburban roadways. The north/south roadway consisted of four northbound lanes and four southbound lanes, with the far-left being a left-turn lane only and the far-right lane being right-turn only. The northbound lanes were straight with a level grade leading to the intersection. The southbound lanes were straight with a level grade. The northbound and southbound lanes were separated by a grassy median. The speed limit for both travel directions was 105 kmph (65 mph) and the intersection was controlled by overhead, electric, flashing beacon traffic signals. At the time of the crash, the weather was clear and the roadway surfaces were dry.
+Vehicle 1, the 2013 Scion tC two-door hatchback, was being driven by the 21-year-old female driver (CIREN case subject) in the lane adjacent to the far-left, northbound travel lane while approaching the intersection from the south. The driver of Vehicle 1 intended to enter the intersection and turn left onto the intersecting roadway to head west.
+Vehicle 2, a 2010 Ford Focus four door sedan, was traveling southbound in the right straight lane, approaching the intersection from the north. The driver of Vehicle 2 intended to continue straight through the intersection and continue traveling south.
+Both vehicles entered the intersection simultaneously and the frontal plane of Vehicle 2 struck the right side plane of Vehicle 1 (Event 1). Both vehicles were redirected to the southwest corner of the intersection. Vehicle 1, while rotating counterclockwise, crossed a concrete island, and departed the roadway at the southwest corner. Vehicle 1 traveled a total of 35.7meters (117 feet) before coming to rest on the roadside, facing northwest. Vehicle 2 traveled 11.5 meters (37.7 feet) and came to rest at the corner of the concrete island, facing the southwest direction. Both vehicles were towed from the scene due to damage sustained in the crash.
+The driver, who was the only occupant of Vehicle 1, was noted to be utilizing her three-point lap and shoulder belt (with retractor pretensioner), and the vehicle was equipped with advanced frontal airbags, seat backrest-mounted torso airbags, and roof rail-mounted curtain airbags. As a result of the first impact, the driver's frontal airbags and side curtain deployed. In addition, the right side curtain and the backrest-mounted airbags deployed. The driver sustained serious injuries and was transported by air to a local trauma center for treatment.
+The driver of Vehicle 2 was transported by land to a local hospital; however, his treatment status was unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>248</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted 45-year-old female driver of a 2012 Toyota Corolla four-door sedan (Vehicle 1), which was primarily involved in a moderate frontal impact with the frontal plane of a 2018 Ford F-150 pick-up truck. Vehicle 1 was equipped with frontal airbags, backrest-mounted side airbags (front outboard positions), and side curtain airbags (for all outboard seating positions).
+This crash occurred during the early morning hours (dark, street lights present) of a summer weekday, on a five lane east/west roadway, at the area of an interchange access ramp. The east/west roadway consists of three westbound through lanes, a dedicated westbound left turn lane to access the interchange ramp (one-way access), and one eastbound through lane. The access ramp intersects the east/west roadway on the south side. At the area of the crash, the roadway is relatively level, but has a left-turning curve for the eastbound travel direction leading into the crash area. The east/west roadway has a speed limit of 64 kmph (40 mph). At the time of the crash, it was raining and the bituminous roadway surface was wet. No traffic controls are present at the crash area.
+Vehicle 1 was traveling westbound, in the westbound left turn lane. The driver of Vehicle 1 intended to turn left and continue traveling southbound via the access ramp. Vehicle 2, the 2018 Ford F-150 pick-up truck, was traveling eastbound, approaching the crash area from the west. The driver of Vehicle 2 intended to continue traveling eastbound.
+Both vehicles entered the intersection at the same time and the frontal plane of Vehicle 2 struck the frontal plane of Vehicle 1 (event 1). As a result of the impact, Vehicle 1 rotated while being redirected back and across the westbound travel lanes. Vehicle one departed the north side of the roadway and struck a curb with its lower frontal plane (event 2) prior to coming to rest partially off road, facing a northeasterly direction. Vehicle 2 departed the southeast corner of the intersection and came to rest facing a southeasterly direction. As a result of the impact with Vehicle 2, Vehicle 1’s driver’s frontal airbag deployed as did both roof rail-mounted side curtain airbags.
+Following the collision, the belted 45-year-old female driver and sole occupant of Vehicle 1 was extricated and transported, by land unit, to a local hospital, but was subsequently transferred to a regional trauma center and hospitalized with minor to critical injuries. Both Vehicle 1 and Vehicle 2 were towed from the scene due to disabling damage sustained during the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>262</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>vehicle_encroachment</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 49-year-old, female driver with deployed frontal airbags. She sustained serious injuries when the five-door hatchback she was driving was involved in a near side angled crash to the right rear plane of a medium/heavy van-based vehicle. No other passengers were in the vehicle.
+The crash occurred during the afternoon hours on a dry road under cloudy skies. The roadway consisted of a two-way, five-lane with center turn lane, suburban road with a posted speed limit of 72 km/h (45 mph). The bituminous road was straight and on a 3 percent downhill grade for the northbound approach, but level in the area of impact. There were no traffic controls in the area of interest.
+A 2012 Freightliner medium/heavy van-based vehicle (V2) was stopped facing north in the center turn lane (lane three) with hazard lights flashing. The vehicle was unoccupied. A 2018 Ford Fiesta hatchback (V1) was traveling north in lane two, intending to continue straight.
+V1 began departing its lane to the left, entering the center turn lane. Upon realizing a crash was imminent, the driver braked and steered right in avoidance. The left forward plane of V1 impacted the right rear corner of V2 (Event 1). Initial contact to V1 was 12 cm aft of the left front bumper corner, making this an angled impact type. However, the PDOF, damage pattern, and injury profile were more reflective of a small overlap frontal crash type. After impact, V1 rotated rapidly counter-clockwise approximately 200 degrees, coming to rest 12 meters from the point of impact, according to police. V2 was pushed forward five meters, as reported by police. V1 was towed due to damage while V2 continued in service.
+The 49-year-old female driver of V1 was presumed to be in an upright position. Based on the driver interview and witness reports, she was suspected of being sleepy and talking on her hands free cell phone at the time of the crash. She was belted as evidenced by an indeterminate amount of shoulder belt payout, five cm of lap belt payout, and loading of the latch plate. The available retractor pretensioner was EDR-reported actuated, although visual confirmation could not be made at inspection due to rescue damage. The vehicle was not equipped with anchor or buckle pretensioners. The steering wheel hub and left knee bolster airbags deployed upon impact. The available right instrument panel, first row outboard seatback, and both curtain airbags did not deploy. No other airbags were installed. This occupant was transported to a trauma center for treatment of serious injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>287</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 59-year-old, female driver with deployed frontal steering wheel-mounted, knee bolster-mounted, seat backrest-mounted, and roof rail-mounted air bags. The driver sustained serious injuries when her intermediate-sized vehicle was involved in a frontal impact (head-on) with a compact utility vehicle.
+The crash occurred during daylight hours on a dry, curved, bituminous, two-lane roadway under clear skies. There was one westbound travel lane (left curve) and one eastbound travel lane (right curve) with a posted speed limit of 89 km/h (55 mph). The westbound travel lane had a pre-crash grade of +3 percent and super-elevation of +3.5 percent. The eastbound travel lane had a pre-crash grade of -3% percent and super-elevation of -6 percent. Both lanes were divided by a double yellow line and there were no traffic control devices.
+A 2011 Chevrolet Cruze (V1) was traveling east, and a 2002 Chevrolet Tracker (V2) was traveling west.
+As V2 was traveling west along the left curve, it crossed over the double yellow line into the eastbound lane and into the path of V1. The front bumper of V1 impacted the front bumper of V2 (Event 1). V1 rotated slightly clockwise from impact, before traveling to its final resting position in the east travel lane (facing east). After initial impact, V2 rotated counterclockwise about 50 degrees while traveling to its final resting position partially off the west travel lane facing southwest. V1 and V2 were both towed from the scene due to damage.
+The 59-year-old female driver (case occupant) was presumed to be seated in an upright position at the time of the impact with V2. This occupant was belted at the time of the crash as evidenced by loading marks on the seatbelt webbing, the pretensioner firing, and the EDR reported the driver’s belt status as “on” at the time of the crash. The steering wheel-mounted, knee bolster-mounted, seat backrest-mounted, and roof rail-mounted airbags all deployed upon impact with V2 (Event 1). The case occupant was transported by ambulance from the scene to a local hospital and then airlifted to a trauma center for treatment of serious injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>310</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>car_following</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 72-year-old, male driver with deployed frontal airbags. He sustained serious injuries when the minivan he was driving was involved in a rear-end crash to a cab chassis pickup truck. The case vehicle was also occupied by a right front passenger whose injury mechanisms were not evaluated. No other passengers were in the vehicle.
+The crash occurred during mid-morning hours in daylight on a dry road under clear skies. The roadway consisted of a divided, northeast/southwest, two-lane, rural highway with a posted speed limit of 89 km/h (55 mph). The bituminous road was straight and on a four percent uphill grade in the southwest direction of travel. There were no traffic controls in the area of interest.
+A 2016 Kia Sedona minivan (V1) was traveling southwest in the right lane of three. A 2015 Chevrolet Silverado cab chassis pickup (V2) was ahead of V1 in the right lane. V2 was a working vehicle picking up debris on the highway in a construction zone. The driver of V2 stopped his vehicle in the travel lane.
+The driver of V1 recognized an impending collision and applied the brakes while steering left in the last moment before impact. V1 slid approximately three meters before the front of V1 struck the back plane of V2 in a rear-end collision with full engagement across the striking planes (Event 1). Both vehicles came to rest approximately two meters from impact. V1 was towed due to damage while V2 continued in service.
+The 72-year-old male driver was presumed to be seated in an upright position. He was belted at the time of the crash as evidenced by an indeterminate amount of shoulder belt payout. The available retractor and anchor pretensioners were actuated with the belt found in the locked and extended (used) position at inspection. The vehicle was not equipped with buckle pretensioners. The steering wheel hub and right top instrument panel airbags deployed upon the Event 1 impact. The available first row outboard seatback and curtain airbags did not deploy. No other airbags were installed. This occupant was transported to a hospital before being transferred to a trauma center for treatment of serious injuries. The 79-year-old, female, right front passenger was belted and had the benefit of a deployed frontal airbag. She was transported to a hospital with non-incapacitating injuries.
+The 50-year-old male driver of V2 was reported to be unbelted with no airbag deployments. He was not injured in the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>341</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 57-year-old, male, right front passenger with deployed front and side airbags. He sustained serious injuries when the compact utility he was riding in was involved in a small overlap frontal crash to a large sedan. The case vehicle was also occupied by a belted, 59-year-old, male driver. He was reported to be uninjured after being evaluated on scene. No other passengers were in the vehicle.
+The crash occurred during mid-afternoon hours in daylight on a dry road under clear skies. The roadway consisted of a two-way, north/south, two-lane, rural highway with a posted speed limit of 89 km/h (55 mph). The bituminous road was straight and on a three percent downhill grade in the southbound direction of travel. It was level for the northbound approach. There were no traffic controls in the area of interest.
+A 2017 Buick Envision compact utility vehicle (V1) was traveling south in lane one. A 2018 Chrysler 300 large sedan was traveling north in lane one when it crossed the centerline to the left into the oncoming lane of travel. V1 braked without lockup and steered left in avoidance.
+V1 and V2 collided in a head-on, small overlap configuration, engaging the right front bumper corners of both vehicles (Event 1). After impact, both vehicles rotated clockwise, coming to rest on the east and west shoulders of the road. Both vehicles were towed due to damage.
+The 57-year-old male right front passenger was presumed to be seated in an upright position. He was belted at the time of the crash as evidenced by 15 cm of shoulder belt payout. The available retractor and anchor pretensioners were actuated with the belt found in the locked and extended (used) position at inspection. The vehicle was not equipped with buckle pretensioners. The steering wheel hub, right top instrument panel, both knee bolster, and both curtain airbags deployed upon the Event 1 impact. The available 1st and 2nd row outboard seatback airbags did not deploy. No other airbags were installed. This occupant was transported to a trauma center for treatment of serious injuries. The belted, 59-year-old male driver was evaluated on scene by emergency medical services and determined to be uninjured.
+The 79-year-old male driver of V2 was reported to be unbelted with deployed front and side airbags. He was transported to a trauma center for treatment of non-incapacitating injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>359</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>This case focuses on the injury mechanisms of a belted 63-year-old female driver of a 2013 Honda Ridgeline pick-up truck (Vehicle 1), which was involved in a moderate twelve-o’clock small overlap frontal impact with the frontal plane of a 2015 Toyota Tacoma pick-up truck (Vehicle 2). Vehicle 1 was equipped with frontal airbags, seat backrest-mounted side airbags (front outboard positions), and side curtain airbags (all outboard seating positions).
+This two-vehicle crash occurred during the morning hours (daylight) of a winter weekday on a rural two-lane north/south roadway. This north/south roadway is relatively straight with slight bends at different locations, but is noted to contain multiple grade transition areas. The roadway is narrow with limited to no shoulder areas. The roadway is bordered by a guardrail on the west side and a wooded area on the east side. At the time of the crash, the weather was clear and the bituminous roadway surface was dry. The speed limit for the roadway at the area of the crash is 56 kmph (35 mph).
+Vehicle 1, the 2013 Honda Ridgeline pick-up truck, was being operated by the 63-year-old female case occupant in the southbound travel lane. The driver, and sole occupant of V1, had just crested a hill with a slight curve and was traveling downhill on a straight section of the roadway. The driver of V1 intended to continue traveling southbound.
+Vehicle 2, the 2015 Toyota Tacoma pick-up truck, was being operated by a 33-year-old male driver in the northbound travel. The driver, and sole occupant, of V2 intended to continue traveling northbound on the straight and graded section of roadway.
+As V2 traveled north, it drifted left and partially entered the southbound travel lane. At this time, the frontal plane of V2 struck the frontal plane of V1 (event 1 – corner to corner small overlap type impact). Both vehicles are believed to have rotated counterclockwise, but to an unknown degree before coming to rest within the confines of the roadway, at or near the area of impact. As a result of the impact, V1’s driver’s frontal airbag deployed, as did the driver’s seat backrest-mounted torso bag and the left side rail curtain. Vehicle 1’s driver’s seat belt retractor pretensioner also actuated as a result of the impact.
+Following the collision, the 63-year-old female driver of V1 was extricated from the vehicle and transported, by ground unit, to a regional trauma center. She was subsequently hospitalized with minor to moderate injuries. The driver of V2 was reported to be uninjured and was not transported from the scene. The extent of his injuries and treatment, if any, are unknown. Vehicle 1 and Vehicle 2 were towed from the scene due to disabling damage sustained in the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>363</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>vehicle_encroachment</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously-injured, belt-restrained, 57-year-old male driver of a 2016 Jeep Wrangler compact utility vehicle, which was primarily involved a left side impact by the front of a 2010 Toyota Corolla four-door sedan. The Jeep was also involved in a subsequent non-horizontal impact to fixed-objects as it rolled following the impact with the sedan. There was also a 4-year-old male passenger in the Jeep that was restrained in a child safety seat, but his seating position is unknown.
+This two-vehicle collision occurred during the late afternoon hours (daylight) on a spring weekday at the intersection of two roadways. The eastbound lanes of the intersection consist of four travel lanes, with two straight lanes, a left turn lane, and a right turn lane. The east and west lanes are separated by opposing grass medians and a center crossover area. The east/west roadway does not have traffic controls. The two-way, two-lane north and south roadway is controlled by opposing stop signs. The posted speed limits are unknown. At the time of the crash, it was raining and the roadway surfaces were wet.
+Vehicle 1, a 2016 Jeep Wrangler compact utility vehicle, was being driven by the 57-year-old male driver (CIREN case subject) in the eastbound lane that is adjacent to the right turn lane while heading east. The driver of Vehicle 1 intended to pass through the intersection and continue traveling east.
+Vehicle 2, a 2010 Toyota Corolla four-door sedan, was stopped in the crossover area of the median heading south.
+Vehicle 1 was passing through the intersection when Vehicle 2 attempted to crossover the eastbound lanes from a stopped position within the crossover area of the median. The driver of Vehicle 1 steered right in an attempted to avoid a collision but was unsuccessful. The front of Vehicle 2 struck the left plane of Vehicle 1 (Event 1). This impact caused Vehicle 1 to rotate clockwise about 135 degrees while departing the roadway to the southeast onto the roadside. Vehicle 1 traveled into a ditch while in a clockwise yaw (left side leading). As the left-side tires of Vehicle 1 entered the ditch-line, Vehicle 1 tripped (Event 2) and began to roll with its left side leading. After rolling one-quarter turn, the rollover was interrupted when the vehicle's top plane struck a 40 cm diameter tree (Event 3) and a 16 cm diameter tree (Event 4). After the impact with the trees, the vehicle slid back down into the ditch and came to rest on its left side, facing west. Vehicle 2 came to rest in the roadway in the eastbound lanes facing southeast. Both vehicles were towed from the scene after sustaining disabling damage.
+The driver of Vehicle 1 was noted to be utilizing his three-point lap and shoulder belt (with retractor pretensioner), and the vehicle was equipped with advanced frontal airbags. As a result of the impact, the driver's frontal airbags deployed. The driver sustained serious injuries and was transported by land to a local hospital. He was later transported by land to a regional trauma center for additional treatment. He was enrolled as a CIREN case subject at the trauma center. The injury and treatment status of the passenger of Vehicle 1 and occupants in Vehicle 2 are unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>406</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a moderately injured, belted, 65-year-old, female driver of a 2014 Toyota Corolla that was involved in an offset-frontal impact with a small utility vehicle. There was also a belted, 5-year-old, male occupant located in the second row left seating position.
+The crash occurred during daylight hours on a dry, bituminous, north/south roadway under clear skies within the confines of a four-legged intersection. The northbound and southbound travel lanes were separated by a raised traffic island. The northbound travel lanes consisted of four travel lanes (two straight lanes, one left turn and one right turn) with a posted speed limit of 72 km/h (45 mph) and a -2.1 percent grade at the point of impact. The southbound travel lanes consisted of four travel lanes (two straight lanes, one left turn and one right turn) with a posted speed limit of 72 km/h (45 mph). The north/south travel lanes were intersected by an entrance/exit to a townhouse community on the west and an entrance/exit ramp to a county highway on the east side. This intersection is controlled by standard tri-colored traffic signals for each direction.
+A 2014 Toyota Corolla (V1) was traveling south in the left turn lane. A 2008 Nissan Rogue (V2) was traveling north in the left through lane.
+As V1 entered the intersection in an attempt to execute a left turn in front of V2, it was impacted on the front-right corner by the front plane of V2 (Event 1). After initial impact, V1 rotated counter-clockwise (approximately 220 degrees) before traveling to final rest, partially on a raised traffic island in the middle of the intersection facing northwest. V2 rotated slightly clockwise before traveling to its final resting position in the northeast quadrant of the intersection. V1 and V2 were towed from the scene due to damage.
+The 65-year-old female driver of V1 (case occupant) was presumed to be seated in an upright position at the time of the impact with V2 (Event 1). The driver was belted at the time of the crash as evidenced by 7 cm of loading marks on the seatbelt webbing and confirmed by EDR data. The frontal steering wheel-mounted, knee bolster-mounted, seat backrest-mounted, and roof rail-mounted curtain airbags all deployed upon impact with V2. This case occupant was transported by ground from the scene to a referring hospital before being transferred by ground to a trauma center for treatment of moderate injuries.
+There was a 5-year-old, male passenger in the second row left seating position at the time of the crash. The passenger was belted in a child safety seat and was reported to be uninjured in the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>408</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously injured, belt restrained, 83-year-old, male, driver of a 2015 Lexus RX 350, compact utility vehicle.
+This two-vehicle collision occurred during daytime hours on an, urban, asphalt roadway. The east/west roadway consists of four travel lanes in each direction. The far right lane is channeled allowing for traffic to turn right into a shopping center or continue straight at the intersection. The far left lane is a dedicated turn lane separated from the other travel lanes by a gore. The eastbound roadway is separated from the westbound roadway by a raised grassy median with a concrete curb. There is a standard overhead, tricolor, traffic control signal at the intersection. The westbound roadway is straight with a five percent uphill grade and a posted speed limit of 72 km/hr (45 mph). The eastbound roadway is straight with a six percent downhill grade. At the time of the crash, the weather was clear and dry.
+Vehicle 1 (V1), a 2015 Lexus RX 350, compact utility vehicle was driving westbound in the left turn lane. The driver of Vehicle 1 intended to turn left at the intersection into a shopping center.
+Vehicle 2 (V2), a 2016 Cadillac SRX, compact utility vehicle was traveling eastbound in the second travel lane approaching the intersection. The driver of V2 intended to continue traveling east.
+Per the crash report, as V2 entered the intersection V1 initiated a left turn causing the front plane of V2 to impact the right front plane of V1. The impact caused V1 to rotate counterclockwise almost one hundred and eighty degrees coming to a final rest on the east side of the in intersection facing slightly northeast. After the impact V2 traveled forward and came to rest between the first and second eastbound travel lanes facing slightly southeast.
+V1 and V2 were towed from the scene due to disabling damage sustained in the crash.
+The driver of V1 was noted to be utilizing his three-point lap and shoulder belt (with retractor pretensioner). The vehicle was equipped with advanced frontal, seatback, knee bolster and roof rail-mounted airbags. As a result of the impact, the steering wheel and driver's knee bolster airbags deployed.
+The driver of V1 sustained injuries and was treated at the scene, but refused transport. He was later taken by a family member, in a private car, to an outside hospital. Due to his injuries, he was transported from the outside hospital by land to a trauma center for treatment and enrolled as the CIREN case occupant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>420</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>This crash case involves a severely injured, belted, 58-year-old, female, right-front passenger of a 2017 Mitsubishi Outlander compact utility vehicle, involved in a right-side impact from a 2019 Hyundai Elantra.
+This two-vehicle collision occurred during daylight hours on an urban, asphalt, four-legged intersection. The northbound roadway consists of four travel lanes with a dedicated right and left turn lane at the intersection. The northbound roadway narrows to two lanes on the north side of the intersection. The southbound roadway consists of four travel lanes with a dedicated right and left turn lane at the intersection. The southbound roadway narrows to three lanes on the south side of the intersection. A raised concrete median separates the north/south roadways. The westbound roadway consists of two lanes on the west side of the intersection. The eastbound roadway consists of two lanes, with the first lane turning into a channelized right turn lane with a raised triangular concrete island, at the intersection. The east/west travel lanes are separated by a raised concrete median on the west side of the intersection. There is a standard tricolored traffic control signal at the intersection. The roadway is straight and level with a posted speed limit of 72 kmph (45 mph). At the time of the crash, the weather was clear and the road surface was dry.
+Vehicle 1 (V1), a 2017 Mitsubishi Outlander compact utility vehicle, was driving northbound in the left turn lane. The driver of V1 intended to turn left (west) and continue traveling west.
+Vehicle 2 (V2), a 2019 Hyundai Elantra, was traveling southbound in the second travel lane. The driver of V2 intended to continue traveling south.
+Per the crash report, V1 initiated a left hand turn as V2 entered the intersection causing the front plane of V2 to impact the right plane of V1 in the area of the front passenger door. As a result of the impact, V1 rotated clockwise approximately ninety degrees while traveling into the westbound roadway where it came to a final rest in the first lane facing northeast. V2 rotated clockwise approximately one hundred degrees coming to a final rest on the southeast side of the intersection facing northwest. V1 and V2 were towed from the scene due to disabling damage sustained in the crash.
+The driver and right-front passenger of V1 were noted to be utilizing their three-point lap and shoulder belts (with retractor pretensioners). The vehicle was equipped with advanced frontal, knee bolster, seat back, and roof rail-mounted airbags. As a result of the impact, the advanced frontal, driver knee bolster, passenger seatback, and passenger roof-rail mounted airbags deployed.
+The right-front passenger of V1 sustained severe injuries and was transported by land to a level-one trauma center where she was admitted and enrolled as the CIREN case occupant. The driver of V1 did not sustain injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>426</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 67-year-old, male driver with deployed front and side airbags. He sustained serious injuries when the compact pickup truck he was driving was involved in a head-on, small-overlap, frontal crash to an intermediate-size wagon. The investigation also focused on the injury mechanisms of a belted, 69-year-old, female, right-front passenger with a deployed front airbag in the same vehicle. She also incurred serious injuries. No other passengers were in the vehicle.
+The crash occurred during morning hours in daylight on a dry road under clear skies. The roadway consisted of a two-way, east/west, two-lane, rural highway with a posted speed limit of 89 km/h (55 mph). The bituminous road was straight and on a 3 percent uphill grade in the eastbound direction of travel. There were no traffic controls in the area of interest.
+A 2014 Nissan Frontier Crew Cab pickup towing a lawn mower trailer (V1) was traveling east in the right lane. A 2002 Ford Taurus wagon (V2) was traveling west in the right lane. A vehicle ahead of V2 was beginning to turn right at an intersecting street. The driver of V2 steered left into the oncoming lane in an attempt to overtake the turning vehicle ahead of it.
+The driver of V1 braked and steered right in an attempt to avoid the impending collision. V1 and V2 collided in a head-on, small overlap configuration (Event 1). V1 traveled off the right side of the road while leaving a long gouge before coming to rest in the south roadside. V2 rotated approximately 100 degrees counter-clockwise, coming to rest perpendicular across the westbound lane of travel. Both vehicles were towed due to damage.
+V1's EDR recorded a +27 km/h longitudinal Delta-V for the frontal impact. This model of Nissan ACM has a known issue which causes the polarity to be recorded as positive in frontal impacts. The value of -27 km/h was agreed upon by all crash engineers as the actual Delta-V experienced at the module.
+The 67-year-old male driver of V1 was presumed to be seated in an upright position. He was belted at the time of the crash, as evidenced by 5 cm of shoulder belt payout, 2 cm of lap belt payout, and loading of the latch plate. The available retractor pretensioner was actuated with the belt found in the locked and extended (used) position at inspection. The vehicle was not equipped with buckle or anchor pretensioners. The steering wheel hub, right top instrument panel, left seatback, and left curtain airbags deployed upon the Event 1 impact. The available right seatback and right curtain airbags did not deploy. No other airbags were installed. This occupant was transported to a trauma center for treatment of serious injuries.
+The 69-year-old female passenger of V1 was presumed to be seated in an upright position. She was belted at the time of the crash, as evidenced by 5 cm of shoulder belt payout and latch plate loading. The available retractor pretensioner was actuated with the belt found in the locked and extended (used) position at inspection. The vehicle was not equipped with buckle or anchor pretensioners. This passenger had the benefit of only the right top instrument panel airbag, which deployed upon the Event 1 impact. The available right seatback and right curtain airbags did not deploy. This occupant was transported to a trauma center for treatment of serious injuries.
+The opposing vehicle (V2) was driven by a 31-year-old female driver who was reported to be belted with only the shoulder belt and protected by front and side airbags. She was transported to a trauma center for treatment of minor injuries. An 8.5-month-old female was restrained in a child seat in the second row middle seat. She was uninjured. A 7-year-old female occupied the second row right seat and was belted. She was transported to a trauma center for treatment of non-incapacitating injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>460</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>lane_departure_same</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously-injured, belted, 51-year-old female driver and a belted, 49-year-old female front passenger of a 2017 Nissan Maxima four-door sedan, involved in a left rear impact with a 2018 Chevrolet Malibu four-door sedan and a subsequent right front impact to a concrete wall barrier/divider.
+This two-vehicle collision occurred during nighttime hours on a dark, but lighted, urban asphalt divided roadway. The roadway ran north/south with three travel lanes in each direction separated by a concrete wall barrier/divider. The roadway had a sweeping left curve. There was a posted speed limit of 89 kmph (55 mph) with no traffic controls. At the time of the crash, the weather was cloudy and the road surface was dry.
+Vehicle 1 (V1), the 2017 Nissan Maxima four-door sedan, was driving south in the second southbound travel lane. The driver of V1 intended to continue driving south. Vehicle 2 (V2), the 2018 Chevrolet Malibu four-door sedan, was traveling south in the third (outer-most) southbound travel lane. The driver of V2 intended to continue traveling south.
+Per the crash report, V2 was traveling at a high rate of speed and exited the third travel lane to the right, crossing into the second travel lane where the right front plane of V2 impacted the left rear plane of V1 (Event 1). As a result of the impact, V1 was pushed forward and rotated counterclockwise over ninety degrees traveling over the third travel lane and the left shoulder where the right front plane of V1 impacted the center concrete divider/barrier wall (Event 2). V1 was redirected off the concrete wall and continued rotating counterclockwise almost another one hundred and eighty degrees and came to rest on the left shoulder facing slightly southwest. As a result of the impact, V2 traveled forward rotating clockwise one hundred and eighty degrees across the second and first travel lanes and the right shoulder where the rear plane struck a concrete barrier wall (Event 3). V2 was redirected off the concrete wall barrier continuing its clockwise rotation and came to rest on the right shoulder facing slightly northwest.
+V1 and V2 were towed from the scene due to disabling damage sustained in the crash.
+The driver and front passenger of V1 were noted to be utilizing their three-point lap and shoulder belt (with retractor and anchor pretensioner). The vehicle was equipped with advanced frontal, seatback, and roof rail-mounted airbags. As a result of the impact, the advanced frontal, driver’s seatback, and both roof rail-mounted airbags deployed.
+The driver and front passenger of V1 sustained serious injuries and were transported by land to a level-one trauma center where they were admitted with moderate injuries and enrolled as CIREN case occupants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>490</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>car_following</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>This crash case involves a moderately- injured, unbelted, 43-year-old, male driver of a 2018 Ford EcoSport compact utility vehicle, which was primarily engaged in a frontal collision with the rear of a 2018 Volvo EW180 Series Excavator.
+Vehicle 1, a 2018 Ford EcoSport compact utility vehicle (V1), was being driven northbound by the 43-year-old male driver (CIREN case subject) in the right lane.
+Vehicle 2, a 2018 Volvo EW180 Series Excavator (V2), was being driven northbound in the right lane, leading Vehicle 1.
+As V1 approached the slower moving V2 from the rear, the driver of V1 steered left and braked in an attempt to avoid the imminent collision. The front plane of V1 struck the rear of V2 (Event1). After impact, V1 traveled left and off the roadway, coming to rest on the left roadside while facing north. V2 pulled ahead after the crash and parked on the right roadside. V1 was towed due to damage sustained in the crash. V2 was not towed or disabled.
+The driver of V1 was not restrained by his three-point lap and shoulder belt (with retractor pretensioner). The vehicle was equipped with advanced frontal airbags (including a driver's knee bolster airbag), seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. As a result of the impact, the driver's steering wheel and knee bolster airbags deployed.
+The 43-year-old male driver sustained moderate injuries, and was transported by land to a nearby hospital. Later he was transferred by land to a regional trauma center where he was enrolled as a CIREN case subject.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>497</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>left_turn_straight</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>This case focuses on the injury mechanisms of a belted 29-year-old male driver of a 2016 Audi S3 four-door sedan (Vehicle 1), who was primarily involved in a severe, twelve-o’clock frontal impact with the frontal plane of a 2016 Toyota Corolla four-door sedan (Vehicle 2). Vehicle 1 was equipped with frontal airbags for the driver and front right passenger positions, driver and front right passenger knee bolster airbags, seat backrest-mounted side airbags for the front outboard seating positions, and side curtain airbags for all outboard seating positions.
+This crash occurred during the evening hours (dark, street lamps present) of a fall weekday, at the intersection of a bituminous, two-lane, north/south residential roadway and a bituminous, two-lane, east/west residential roadway. Approaching the intersection from the south, the northbound travel direction has a positively graded sweeping right-turning curve which transitions to a left-turning curve at the north side of the intersection. Approaching the intersection from the north, the southbound travel direction has a negatively graded right-turning curve. There are no traffic controls at the intersection for the north/south roadway. All roadways are curbed with single-family residential housing units occupying the roadsides. At the time of the crash, the weather was clear and the roadway surfaces were dry. The speed limit in the vicinity of the crash site is 40 kmph (25 mph).
+Vehicle 1, the 2016 Audi S3 four-door sedan, was traveling northbound, approaching the intersection from the south. The belted 29-year-old male driver, and sole occupant, intended to negotiate the curved section of roadway, pass through the intersection, and continue traveling northbound.
+Vehicle 2, a 2016 Toyota Corolla, was being operated by a 17-year-old female driver, and sole occupant, in the southbound travel lane, approaching the intersection from the north. The driver of Vehicle 2 intended to turn left at the intersection in order to continue traveling eastbound.
+As Vehicle 2 slowed and initiated its left turn, in a somewhat shallow travel path, the driver of Vehicle 1 braked, but was unsuccessful in avoiding a collision. The frontal plane of Vehicle 1 struck the frontal plane of Vehicle 2 in a head-on fashion (event 1) within the northbound travel lane near the northern leg of the intersection. As a result of the impact, Vehicle 2 rotated counterclockwise, striking the curbed edge of the northeast corner of the intersection (event 2) before coming to rest in the northbound travel lane, north of the intersection, facing an easterly direction. Vehicle 1 was redirected to the northeast corner of the intersection where it struck the curbed edge of the roadway with its lower frontal plane and wheels (event 3) before partially departing the roadway. Vehicle 1 came to rest at the northeast corner of the intersection, facing a northeasterly direction. As a result of the first event, Vehicle 1’s driver’s frontal airbag deployed, as did the driver’s knee bolster airbag, and the driver’s seat belt pretensioner actuated.
+Following the collision, the belted 29-year-old male driver of Vehicle 1 was able to self-extricate himself from the vehicle. He was not transported from the scene, and returned home. Several days later, the driver of Vehicle 1 presented himself at a local hospital, but was transferred to a regional trauma center and hospitalized with serious injuries sustained in the crash. The 17-year-old female driver of Vehicle 2 was transported, by ground unit, to a local hospital with suspected minor injuries; however, the extent of her injuries and treatment, if any, are unknown. Both vehicles were towed due to damage sustained in the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>559</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 22-year-old, female, driver with deployed front and side airbags. She sustained moderate injuries when the intermediate sedan she was driving was involved in a head-on collision to an intermediate coupe. No other passengers were in the vehicle, but an 8-week-old dog was present in the right front seat.
+The crash occurred during early afternoon hours on a wet road under cloudy skies. The roadway consisted of a two-way, north/south, two-lane, residential road with a posted speed limit of 56 km/h (35 mph). The bituminous road was straight and on a 5 percent downhill grade in the northbound direction of travel. The southbound direction was curved right with 10 percent superelevation, attributable to roadway crown, and on a 3 percent uphill grade.
+A 2016 Mazda 3 sedan (V1) was traveling north in the right lane intending to continue straight. A 2014 Ford Mustang coupe (V2) was traveling southbound negotiating the right curve while fleeing a pursuer at a high rate of speed. V2 lost control of the vehicle and begin yawing back and forth, eventually encroaching into the oncoming lane of travel. V1 began panic braking, leaving 22 meters of tire impressions pre-impact according to police.
+V1 and V2 collided in a head-on, full-frontal configuration (Event 1), slightly offset towards the passenger side of each vehicle. The impact caused both vehicles to rapidly rotate clockwise. V1 rotated approximately 300 degrees before coming to rest in the adjacent southbound lane. V2 rotated approximately 180 degrees while departing the east side of the road. V2’s motion was slowed by either the curb or tire friction on the east roadside, causing it to roll right one quarter-turn (Event 2), where it came to rest. Both vehicles were towed due to damage.
+The 22-year-old female driver of V1 was presumed to be seated in an upright position. Her left hand was on the steering wheel and her right arm was outstretched to restrain the puppy in the right front seat. She was belted at the time of the crash as evidenced by 16 cm of shoulder belt payout, 4 cm of lap belt payout, and loading of the latch plate. The available retractor and anchor pretensioners were actuated with the belt found in the locked and extended (used) position at inspection. The vehicle was not equipped with buckle pretensioners. The steering wheel hub and right curtain airbags deployed upon the Event 1 impact. The available right instrument panel, first row outboard seatback, and left curtain airbags did not deploy. No other airbags were installed. This occupant was transported to a trauma center for treatment of moderate injuries.
+The 27-year-old male driver of V2 was reported by police to be belted with front and side airbag deployments. He was transported to a trauma center for treatment of non-incapacitating injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>594</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted 47-year-old female driver with deployed frontal steering wheel-mounted and knee bolster-mounted airbags. There was also a belted 15-year-old female front right passenger with deployed frontal instrument panel mounted airbag. The driver sustained serious injuries when the four door minivan (V1) she was in was involved in a frontal impact with a four door subcompact vehicle (V2).
+This crash occurred during daylight hours on a dry, bituminous divided trafficway (median strip without positive barrier) under clear skies. There were four east travel lanes (two through lanes, one left turn and one right turn) and four west travel lanes (two through lanes, one left and one right). The east lanes have a slight right curve and the west lanes curve slightly to the left. Both east/west travel lanes were level grade at point of impact and divided by a grass median. The speed limit at this location is 80km/h (50 mph). The intersecting north/south roadway consisted of one north travel lane and three south travel lanes (one through lanes, one left and one right). These travel lanes were divided by a raised concrete median on the northern side of the intersection. This intersection is controlled by overhead traffic signals.
+A 2017 Dodge Grand Caravan (V1) was traveling east in the left turn lane and a 2006 Nissan Sentra (V2) was traveling west in the left through lane.
+As V1 was traveling east it attempted to execute a left turn to travel north when its front bumper impacted the front bumper of V2 (Event 1). After initial impact, V1 rotated counterclockwise approximately 80 degrees before traveling to its final resting position in the middle of the intersection facing north. V2 was traveling west in the left through lane and attempting to travel through the intersection when its front bumper impacted the front bumper of V1. After initial impact V2 rotated clockwise approximately 20 degrees before traveling to its final resting position in the middle of the intersection facing northwest. V1 and V2 were towed from the scene due to damage sustained in the crash.
+The 47-year-old female driver (V1/occupant 1) was presumed to be seated in an upright position at the time of impact. The driver was belted as evidenced by loading marks to the seatbelt webbing observed during vehicle inspection, the EDR, and injuries sustained in the crash. The frontal steering wheel-mounted and knee bolster-mounted airbags both deployed upon impact (Event 1) with V2. This CIREN case occupant was transported by ground ambulance from the scene to a local hospital and then later transferred (by ground ambulance) to a local trauma center for treatment of serious injuries.
+The belted 15-year-old female front right passenger non-case occupant (V1/occupant 2) was presumed to be seated in an upright position at the time of the impact. She was belted as evidenced by the vehicle inspection and the EDR. The frontal instrument panel mounted airbag deployed upon impact with V2. This occupant was not injured in the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>597</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously injured, unbelted, 40-year-old male driver of a 2018 Ford Explorer, mid-size utility vehicle with rear kennel compartment, involved in a frontal collision.
+This two-vehicle collision occurred during early morning hours on a dark, not lighted, semi-rural, asphalt roadway. The roadway runs primarily north/south with two travel lanes in each direction and a center turn lane. The roadway is straight for southbound travel and curved left for northbound travel. There is a greater than two percent downhill grade for southbound traffic and greater than two percent uphill grade for northbound traffic. The posted speed limit is 89 kmph (55 mph) without traffic controls. At the time of the crash, the weather was rainy and the road surface was wet.
+Vehicle 1 (V1), a 2018 Ford Explorer mid-size utility vehicle, was driving south in the second (left) southbound travel lane. The driver of V1 intended to continue driving south.
+Vehicle 2 (V2), a 2004 Ford Explorer Sport Trac compact pickup truck, was traveling north in the second northbound (left) travel lane. The driver of V2 intended to continue traveling north.
+Per the crash report, V2 hydroplaned on the wet roadway causing the vehicle to rotate counterclockwise, crossing the second northbound lane, the center turn lane and into the second southbound travel lane where it entered the path of V1. The right front plane of V1 impacted the left front plane of V2 (Event 1). As a result of the impact, V1 traveled across the southbound lanes and onto the east shoulder where it struck a culvert (Event 2). V1 came to a final rest on the east shoulder facing south. As a result of the impact, V2 tripped into a left leading, five-quarter-turn roll and came to a final rest with the driver’s side down on the west shoulder facing west.
+V1 and V2 were towed from the scene due to disabling damage sustained in the crash.
+The driver of V1 was not utilizing the three-point lap and shoulder belt (with retractor pretensioner). The vehicle was equipped with advanced frontal, seatback, and roof rail-mounted airbags. As a result of the impact, the steering wheel, drivers seatback (impinged), and both roof rail-mounted airbags deployed.
+The driver of V1 sustained serious injuries and was transported by land to a level-one trauma center where he was admitted and enrolled as the CIREN case occupant. The driver of V2 was transported to a local hospital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>634</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of an unbelted 11-year-old male second row right passenger with deployed roof rail-mounted airbag. The second row right passenger sustained critical injuries when the intermediate four-door sedan he was in was involved in an off-set frontal impact with another intermediate four-door sedan.
+There was one other passenger in the vehicle at the time of the crash, a belted 32-year-old female driver with deployed frontal steering wheel-mounted, knee bolster-mounted, seat backrest-mounted torso/pelvis, and roof rail-mounted curtain airbags.
+The crash occurred during the morning hours (daylight) on a wet, bituminous two-lane roadway under cloudy skies within a sag in the roadway. There was one westbound travel lane (hard curve to the right) and one eastbound travel lane (slight curve to the left) with a posted speed limit of 72 km/h (45 mph). The west travel lane has a pre-crash grade of -9 percent. The east travel lane has a pre-crash grade of +1.4 percent. Both lanes were divided by a double yellow line and there were curve warning signs leading up to and through each direction's curve.
+A 2018 Toyota Corolla (V1) was traveling east and a 2015 Dodge Dart (V2) was traveling west.
+V1 was traveling eastbound when V2 crossed over the double yellow line and impacted its front with the front of V1. According to the EDR, the driver of V1 applied the brake prior to impact. The driver of V1 also steered right then left prior to impact. After initial impact V1 rotated clockwise about 80 degrees before traveling to its final resting position in the westbound travel lane facing southeast. V2 was traveling westbound and, after rounding the hard right curve, traveled over the double yellow line and impacted its front with the front of V1. After initial impact V2 traveled partially off the east road edge impacting a guardrail before traveling to final rest facing west. V1 and V2 were towed from the scene due to damage.
+The 11-year-old male second row right passenger (case occupant) was presumed to be seated in an upright posture at the time of the impact with V2. This passenger was not using the available three-point belt restraint at the time of the crash. The roof rail-mounted curtain airbags deployed upon impact (Event 1) with V2. This case occupant was transported by ground ambulance to a local hospital and then transferred to a trauma center by air ambulance for treatment of critical injuries.
+The 32-year-old female driver (non-case occupant) was presumed to be seated in an upright position at the time of the impact with V2. The driver was using the three-point belt restraint and the frontal steering wheel-mounted, knee bolster-mounted, seat backrest-mounted, and roof rail-mounted curtain airbags deployed upon impact (Event 1) with V2 as evidenced by the EDR and vehicle inspection. This occupant was transported by ground from the scene to a local hospital for treatment of minor injuries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>664</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>left_turn_straight</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously injured, belted, 74-year-old, female driver of a 2014 Ford Focus four-door sedan, which was primarily involved in a frontal impact with a 2007 Honda Fit five-door hatchback.
+This two-vehicle collision occurred on a two-way, two-lane roadway during the dusk hours on a cloudy day. This dry asphalt roadway curved to the right when traveling from south to north and was intersected by a two-way, two-lane asphalt road at the eastern edge of the north/south lanes. The north lane had a level grade and the south lane had a negative grade. The posted speed limit for the roadway was 89 kmph 55 mph.
+Vehicle 1, a 2014 Ford Focus four-door sedan, was being driven northbound (south to north) by the 74-year-old female driver (CIREN case subject).
+Vehicle 2, a 2007 Honda Fit five-door hatchback, was being driven southbound (north to south).
+Vehicle 1 attempted to travel through the intersection while Vehicle 2 attempted to turn left onto an intersecting road. The driver of Vehicle 1 braked and steered right in an attempt to avoid the impending collision. The front of Vehicle 1 contacted the front of Vehicle 2 (Event 1). After impact, Vehicle 1 was redirected northeast while rotating counterclockwise. Vehicle 1 departed the roadway onto the roadside adjacent to the northbound lane and came to rest facing northwest. Vehicle 2 was redirected north and came to rest in the northbound lane facing northeast. Both vehicles were towed from the crash site due to disabling damage.
+The driver of Vehicle 1 was restrained by her three-point lap and shoulder belt (with retractor and anchor pretensioners), and the vehicle was equipped with advanced frontal airbags, seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. The driver's frontal (including knee airbag) and curtain airbags deployed.
+The driver sustained serious injuries and was transported by air to a level one trauma center and enrolled as a CIREN case subject.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>687</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously-injured, belted 74-year-old female driver of a 2018 Ford Escape utility vehicle primarily engaged in an oblique frontal impact with a 2020 Ford Escape utility vehicle.
+This two-vehicle collision occurred at the intersection of an eight-lane divided trafficway and a two-lane roadway during daytime hours. The roads were asphalt, dry, and controlled by traffic signals. There were four lanes for the northbound and southbound traffic, including left and right turn-only lanes for both travel directions. The northbound lanes were level and the southbound lanes had a grade of 2%. The speed limit was 72 kmph (45 mph) in the north/south lanes.
+Vehicle 1, a 2018 Ford Escape utility vehicle, was traveling northbound (south to north) in the left turn lane. It was being driven by the 74-year-old female who is the CIREN case subject.
+Vehicle 2, a 2020 Ford Escape utility vehicle, was traveling southbound (north to south) in the outside straight-through lane.
+As V1 attempted to turn left at the intersection, its front was contacted by the front of V2 (Event 1). After impact, both vehicles were redirected slightly southwest. After the initial contact, V1 rotated counterclockwise while V2 rotated clockwise. Vehicle 1 came to rest facing southwest and V2 came to rest facing west. Both vehicles were towed from the crash site due to disabling damage.
+The driver of V1 was restrained by her three-point lap and shoulder belt (with retractor and anchor pretensioners), and the vehicle was equipped with advanced frontal airbags, seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. The driver's frontal (including knee airbag) and curtain airbags deployed. With the exception of the passenger's frontal airbag, all right side airbags deployed.
+The driver sustained serious injuries and was transported by ground to a local hospital. She was later transferred to a level 1 trauma center where she was enrolled as a CIREN case subject.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>718</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>vehicle_encroachment</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously injured, unbelted, 44-year-old, female driver of a 2019 Nissan Altima four-door sedan, primarily engaged in a frontal impact with the rear of a 2019 International 7400 Medium/Heavy dump truck.
+This two-vehicle collision occurred on a two-lane, two-way asphalt roadway during the morning hours (daylight). On this east/west road, the eastbound lane had an uphill grade and was dry, and the posted speed limit was 89 kmph (55 mph).
+Vehicle 1, a 2019 Nissan Altima four-door sedan, was driven by the 44-year-old female CIREN case subject in the eastbound lane. This vehicle was traveling eastbound.
+Vehicle 2, a 2019 International 7400 Medium/Heavy dump truck, was stopped partially in the eastbound travel lane and partially off the roadway behind another stalled dump truck.
+A flagman was standing on the double-yellow lane line adjacent to Vehicle 2, directing traffic.
+As Vehicle 1 approached Vehicle 2, the driver of Vehicle 1 was blinded by the sunlight and did not initially notice the stopped vehicles or the flagman directing traffic. However, at the last moment, the driver of Vehicle 1 saw the stopped dump truck, steered left, and applied her brakes. The right-front of Vehicle 1 struck the rear of Vehicle 2. After impact, Vehicle 1 was redirected northeast while rotating clockwise. Vehicle 1 crossed the westbound lane before departing the roadway, where it came to rest in a ditch facing south. Vehicle 2 moved slightly forward after impact and came to rest facing east while partially in the eastbound lane and partially off the roadway. The vehicles were towed from the crash site due to disabling damage.
+The driver of Vehicle 1 was not using her three-point lap and shoulder belt (with retractor pretensioner), and the vehicle was equipped with advanced frontal airbags, seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. As a result of impact, the driver's frontal (including knee bolster airbag) and right side curtain airbags deployed.
+The driver sustained serious injuries and was transported by land in a private vehicle to a nearby hospital. She was later transferred by land to a level one trauma center, where she was enrolled as a CIREN case subject.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>732</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>car_following</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 80-year-old, male driver with a deployed front airbag. He sustained moderate injuries when the compact sedan he was driving was involved in a rear-end collision to a compact pickup truck. No other passengers were in the vehicle.
+The crash occurred during mid-morning hours on a dry road under clear skies. The roadway consisted of a two-way, north/south, two-lane, rural highway with a posted speed limit of 72 km/h (45 mph). There was an entrance to a parking lot on the west side of the road. The bituminous road was straight with a 2 percent downhill grade at the area of impact. The approach was on a hillcrest. There was a speed limit sign with digital readout of passing vehicles’ speeds for northbound traffic.
+A 2018 Nissan Versa sedan (V1) was traveling north in the right lane, passing over the hillcrest. A 2019 Nissan Frontier pickup (V2) was stopped ahead of V1 in the same travel. It is unknown if the driver of V2 was waiting for other traffic ahead or waiting to turn left into the driveway at the area of impact.
+The front of V1 impacted the back plane of V2 in a rear-end configuration (Event 1), leaving a 30 cm gouge in the road. V1 and V2 traveled a short distance in the northbound lane before coming to rest in the roadway. V1 was towed due to disabling vehicle damage. V2 was removed by its owner.
+The 80-year-old male driver of V1 was presumed to be seated in an upright position. He was belted at the time of the crash as evidenced by an indeterminate amount of shoulder belt and 8 cm of lap belt loading evidence, as well as loading of the latch plate. The latch plate tongue type was free-falling. The available retractor pretensioner was actuated with the belt found in the locked and extended (used) position at inspection. The vehicle was not equipped with anchor or buckle pretensioners. The steering wheel hub airbag deployed upon the Event 1 impact. The available right instrument panel, first row seatbacks, and both curtain airbags did not deploy. No other airbags were installed. This occupant was transported to a hospital before being transferred to a trauma center for treatment of moderate injuries.
+V2 was driven by a 40-year-old female who was reported as being belted with a deployed front airbag. She incurred minor injuries and refused treatment at the scene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>802</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 27-year-old, male driver with deployed frontal airbags. He sustained moderate injuries when the minivan he was driving was involved in a head-on collision to an intermediate sedan. No other passengers were in the vehicle.
+The crash occurred during late afternoon hours in daylight on a dry road under clear skies. The roadway consisted of a two-way, northeast/southwest, two-lane, rural highway with a posted speed limit of 89 km/h (55 mph). The bituminous road was curved left in the southwest-bound direction of travel with +1 percent superelevation and on a 4 percent downhill grade. There were no traffic controls in the area of interest.
+A 2018 Dodge Grand Caravan minivan (V1) was traveling southwest in the right lane negotiating the left curve. A 2003 Ford Taurus sedan (V2) was traveling northeast in the right lane negotiating the right curve. The driver of V2 attempted to pass a non-contact vehicle, moving into V1’s lane of travel.
+The driver of V1 braked, traveled partially onto the right shoulder, then steered left in avoidance. V2 appeared to lose control, as it also traveled partially on the shoulder before returning to the road. V1 and V2 collided in a head-on, full-frontal configuration (Event 1). V1 was pushed back a police-estimated three meters from impact. Both vehicles came to rest in the road and were towed due to disabling vehicle damage.
+The 27-year-old male driver of V1 was presumed to be seated in an upright position. He was belted at the time of the crash as evidenced by 27 cm of shoulder belt and an indeterminate amount of lap belt loading evidence, as well as loading of the latch plate and D-ring. The latch plate tongue type was free-falling. The available retractor and buckle pretensioners were actuated with the belt found in the locked and extended (used) position at inspection. The vehicle was not equipped with anchor pretensioners. The steering wheel hub, right top instrument panel, and left knee bolster airbags deployed upon the Event 1 impact. The available first row seatback and curtain airbags did not deploy. No other airbags were installed. This occupant was transported to a trauma center for treatment of moderate injuries.
+V2 was driven by a 31-year-old female who was reported belted with deployed front and side airbags. She incurred incapacitating injuries and was transported to a trauma center from the scene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>972</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>vehicle_encroachment</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>This case focuses on the injury mechanisms of a belted 43-year-old male driver of a 2018 Volvo S90 four-door sedan (Vehicle 1), who was involved in a severe, twelve-o’clock frontal impact with the left side plane of a 2022 International model MV607 medium box truck (Vehicle 2). Vehicle 1 was equipped with driver and passenger frontal airbags, a driver’s knee bolster airbag, seat backrest-mounted side hip/torso airbags (front outboard positions) and side curtain airbags (for all outboard seating positions).
+This two-vehicle crash occurred during the early evening hours (daylight), of a spring weekday, at the intersection of a bituminous two-lane, east/west roadway and a bituminous, four-lane northbound roadway. The northbound roadway, approaching the intersection from the south, had a right-turning curve and consisted of two northbound through lanes, a dedicated left-turn lane, and a dedicated right-turn lane. The east/west roadway was straight and consisted of two travel lanes, one for each travel direction. Both roadways were level. The eastern leg of the intersection intersected the northbound roadway at a slightly greater than ninety-degree angle (slightly obtuse). Traffic entering the intersection from the east/west roadway was controlled by overhead, standard electric single-unit, red flashing signals, as well as posted “stop” signs. Traffic controls for the northbound roadway consisted solely of standard electric single-unit, yellow flashing signals. The northbound roadway had a speed limit of 89 kmph (55 mph) while the east/west roadway had a speed limit of 80 kmph (50 mph). At the time of the crash, the weather was clear and the roadway surfaces were dry. The overall environment was rural.
+Vehicle 1, the 2018 Volvo S90 four-door sedan, was traveling north, at a constant speed, in the right northbound through lane, approaching the intersection from the south. The belted 43-year-old male driver (case occupant) intended to pass through the intersection and continue traveling north. Occupying the right front seating position was an unbelted 48-year-old male passenger.
+Vehicle 2, a 2022 International MV 607 medium straight truck (configured as a “box truck”), was stopped at the eastern leg of the intersection, facing west. The driver, and sole occupant of Vehicle 2, intended to pass through the intersection and continue traveling west.
+Vehicle 1 and Vehicle 2 entered the intersection at relatively the same time and subsequently collided with Vehicle 1’s frontal plane striking Vehicle 2’s left side plane, specifically in the area of the left rear axle (event 1). Both vehicles subsequently came to rest within the intersection at or very close to the area of impact. As a result of this impact (event 1), Vehicle 1’s driver’s frontal and knee bolster airbags deployed, as did the passenger’s frontal airbag.
+Following the collision, responding fire/rescue and emergency medical personnel assisted and removed both occupants of Vehicle 1. The driver of Vehicle 1, the belted 43-year-old male driver (case occupant) was transported, by air unit, to a regional trauma center and hospitalized with minor to moderate injuries. The unbelted, 48-year-old male passenger of Vehicle 1 was transported, by ground unit, to a local hospital with possible injuries; however, the extent of his injuries and treatment, if any, are unknown. The driver of Vehicle 2 was reported to be uninjured. Both Vehicle 1 and Vehicle 2 were towed from the scene due to damage sustained in the crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>This investigation focused on the injury mechanisms of a belted, 64-year-old, male driver with deployed front and side airbags. He sustained moderate injuries when the compact utility he was driving was involved in an offset frontal crash with a compact pickup.
+The case vehicle was also occupied by a belted, 57-year-old, female, right-front passenger with deployed front and side airbags whose injury mechanisms were evaluated. She incurred severe injuries in the crash. No other passengers were in the vehicle.
+The crash occurred midday on a dry road under clear skies. The roadway consisted of a two-way, north/south, two-lane, suburban road with a posted speed limit of 72 km/h (45 mph). The bituminous road was curved right in the northbound direction of travel with +2% superelevation in the curve and on level grade. A speed limit sign was posted for northbound traffic, with no other traffic controls in the pre-crash approach for either direction. A three-leg intersection with a side street to the east extended from this main road, but did not play a role in the crash.
+A 2019 Cadillac XT5 compact utility (V1) was traveling north in the right lane of two, intending to continue negotiating the right curve. A 1999 Ford Ranger compact pickup (V2) was traveling south in the right lane, intending to continue negotiating the left curve. V2 crossed the double-yellow center line into V1’s path of travel.
+V1 and V2 collided in a head-on, offset frontal configuration (Event 1), causing severe damage to both vehicles. After impact, V1 came to rest just east of impact on the shoulder. V2 was pushed back a few meters to the east shoulder as well. Both vehicles were towed due to disabling vehicle damage.
+The 64-year-old male driver of V1 was presumed to be seated in an upright position. He was belted at the time of the crash, as evidenced by 23 cm of D-ring transfer and 1 cm of latch plate transfer to the belt webbing, as well as loading of the D-ring. The latch plate tongue type was a dynamic locking cam. The available retractor and anchor pretensioners actuated, with the belt found in the locked and extended (used) position at inspection. The vehicle was not equipped with buckle pretensioners. The steering wheel hub, right top instrument panel, left knee bolster, and both curtain airbags deployed in the Event 1 impact. The available first row outboard seatback airbags did not deploy. No other airbags were installed. This occupant was transported to a trauma center for treatment of moderate injuries.
+The 57-year-old, female, right front passenger of V1 was presumed to be seated in an upright position. She was belted at the time of the crash, as evidenced by 10 cm of D-ring transfer and 2 cm of latch plate transfer to the belt webbing, as well as loading of the D-ring. As for the driver, the latch plate tongue type was a dynamic locking cam, the available retractor and anchor pretensioners actuated, and the belt was found in the locked and extended (used) position at inspection. This occupant was transported to a trauma center for treatment of severe injuries.
+V2 was driven by a 45-year-old male who was reported belted with deployed front airbags. He was listed with non-incapacitating injuries and taken to a hospital for treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1034</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously injured, belted, 84-year-old, male driver of a 2020 Chevrolet Equinox utility vehicle (V1), which was primarily involved in a far-side impact with the frontal plane of a 2014 Nissan Sentra four-door sedan (V2).
+This two-vehicle collision occurred in the morning hours on a divided highway. At the time of the collision, the area was clear and dry and daylit. The collision occurred at an intersection, and the trafficway consisted of a north-south divided roadway as well as an east-west roadway. The northbound section of the roadway consisted of four lanes, two through lanes, one left turn lane, and one right turn lane. The southbound section consisted of four lanes, two through lanes, one left turn lane, and one right turn lane. There was a grass median dividing the northbound section from the southbound section. The intersection was controlled by a traffic signal. The posted speed limit for the north-south roadway was 89 km/h (55 mph).
+The 2020 Chevrolet Equinox (V1) was traveling southbound in the left turn lane attempting to proceed eastbound after the turn. A 2014 Nissan Sentra (V2) was traveling northbound in the right through lane. As V1 entered the intersection to turn left, the front right side of V1 and the frontal plane of V2 impacted one another. After impact, V1 moved primarily northeast and rotated counterclockwise before coming to rest on the northeast corner of the roadway facing west. V2 moved primarily northeast and rotated clockwise before coming to rest on the eastern portion of the roadway. Both vehicles were towed from the scene due to disabling damage.
+The 84-year-old male driver of V1 is presumed to have been seated in an upright position. He was belted at the time of the crash, evidenced by loading marks on the chest portion of the three-point belt as well as the EDR data. The driver’s roof side rail airbag did deploy, as did the passenger’s roof side rail and outboard seatback airbag. The steering wheel hub, driver’s outboard seatback, and passenger instrument panel bag were available but not deployed. The occupant was transported by land to a local trauma center for treatment where he was enrolled as a CIREN case occupant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1078</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>vehicle_encroachment</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>This crash involves a severely injured, belted 37-year-old female driver in a 2022 Kia Rio four-door sedan that struck a 2016 Chevrolet Silverado 2500HD pickup truck in the left side with its front.
+This two-vehicle mid-winter afternoon crash (daylight) occurred at the intersection of a four-lane trafficway divided by a grass median and a two-lane roadway controlled by stop signs. The southbound lanes were asphalt, dry, and had a level grade. These lanes curved to the left when traveling from north to south. The two-lane roadway running east to west was asphalt and straight, and the eastbound lane had an uphill grade at the intersection. The weather was clear, and the posted speed limit was 105 kmph (65 mph) for the southbound trafficway and 72 kmph (45 mph) for the east/west roadway.
+The belted 37-year-old female driver in Vehicle 1, the 2022 Kia Rio four-door sedan, is the CIREN case subject. She was in her first trimester of pregnancy. Vehicle 1 traveled north to south, in the outside lane, overtaking a slower-moving non-contact vehicle traveling ahead.
+Vehicle 2, a 2016 Chevrolet Silverado 2500HD pickup truck, was stopped at the west leg of the intersection in the eastbound lane at the stop sign.
+Vehicle 1 moved left into the inside lane and began to overtake the non-contact vehicle. At the same time, Vehicle 2 left the stop sign and attempted to cross over the southbound lanes to enter the median crossover. Vehicle 1 struck the left side of Vehicle 2. After impact, both vehicles were redirected southeast and traveled a short distance. Vehicle 1 came to rest in the median crossover facing southeast. Vehicle 2 rotated counterclockwise before also coming to rest in the median crossover. Vehicle 2 faced northwest at final rest. Both vehicles were towed from the crash scene due to disabling damage.
+The driver of Vehicle 1 used her three-point lap and shoulder belt with a free-falling latch plate. The belt had anchor and retractor pretensioners. Additionally, the vehicle was equipped with advanced frontal airbags, first-row seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. The driver's frontal and right-side airbags were deployed due to the crash. The driver in Vehicle 1 sustained severe injuries and was transported by air to a level-one trauma center.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1089</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>This crash involves a seriously injured, belted 45-year-old male right front passenger in a 2016 Dodge Challenger two-door sedan that was struck in its front by the front of a 2017 Jeep Wrangler utility vehicle. There was also a belted female driver who is not a CIREN case subject.
+This two-vehicle mid-morning crash (daylight) occurred on a two-way five-lane asphalt road running east to west. The road's eastbound lanes were intersected by a two-way two-lane asphalt roadway controlled by a stop sign. The west leg of the intersection was comprised of five lanes. There were two straight-through lanes, a center two-way left turn lane, and two eastbound lanes. The two-way left turn lane turned into a painted divider near the intersection. The intersection's east leg was comprised of two westbound lanes, one left turn lane, and two eastbound lanes. The roads were dry, and the weather was clear. The travel gradients were flat, and the posted speed limit was 72 kmph (45 mph).
+The belted 45-year-old male right front passenger in Vehicle 1, the 2016 Dodge Challenger, is the CIREN case subject. Vehicle 1 traveled west to east in the inside straight-through lane attempting to cross the intersection and continue straight.
+Vehicle 2 was being driven east to west in the inside straight-through lane attempting to continue straight.
+Vehicle 2 drifted left into the left turn lane as it approached the intersection. As it entered the intersection it crossed into the path of Vehicle 1. The driver of Vehicle 1 noticed the impending danger, so she steered left and braked in an attempt to avoid a collision. The front of Vehicle 2 struck the front of Vehicle 1 (Event 1). Vehicle 1 was redirected rearward while it rotated counterclockwise and came to rest on the painted divider facing southeast. Vehicle 2 was redirected northeast while rotating clockwise after impact and came to rest in the outside eastbound lane, facing northeast.
+The right front passenger of Vehicle 1 used his three-point lap and shoulder belt equipped with a free-falling latch plate. The belt was equipped with retractor and buckle pretensioners. Additionally, the vehicle was equipped with advanced frontal airbags, first-row seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. The driver and passenger's frontal airbags, right seat-mounted airbag, and right side curtain airbags deployed due to the crash. The driver was also restrained using her three-point lap and shoulder belt with retractor and buckle pretensioners.
+The right front passenger sustained serious injuries and was transported by air to the nearest level-one trauma center.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1098</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>left_turn_turn</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>This crash involves a seriously-injured, belted 52-year-old female driver in a 2017 Lincoln MKX midsize utility vehicle struck in the front by a 2018 Nissan Altima four-door sedan.
+This two-vehicle crash occurred at an intersection of two two-way trafficways. The north/south trafficway was separated by a grass median on the north leg and a curb median on the south leg. The north side had four asphalt southbound lanes, including two straight-through lanes, a right turn-only lane, a left turn-only lane, and two northbound lanes. The south side had three asphalt northbound lanes, with one left turn-only lane and two straight-through lanes. The west leg of the intersection had five lanes, with two westbound and three eastbound lanes. The east leg of the intersection had one westbound lane and one eastbound lane. The posted speed limit was 64 kmph (40 mph), and the travel lanes had level gradients. The intersection was controlled by traffic signals.
+The belted 52-year-old female driver in Vehicle 1, the 2017 Lincoln MKX midsize utility vehicle, is the CIREN case subject. Vehicle 1 traveled in the left turn lane on the northbound side of the road heading south to north. The driver was attempting to turn left at the intersection to head west. Vehicle 2 was being driven north to south in the right straight through lane attempting to cross over the intersection and continue heading south.
+Both vehicles entered the intersection causing the front of Vehicle 1 to contact the front of Vehicle 2 (Event 1). After this initial impact, Vehicle 1 was redirected south while rotating counterclockwise causing its right rear to strike the left side of Vehicle 2 (Event 2). Both vehicles came to rest in the intersection facing in a southerly direction. Vehicle 1 was towed from the crash scene but did not sustain disabling damage. Vehicle 2 was towed due to disabling damage.
+The driver of Vehicle 1 used her three-point lap and shoulder belt equipped with a dynamic locking latch plate. The belt had retractor and anchor pretensioners. Additionally, the vehicle was equipped with advanced frontal airbags, first-row seat backrest-mounted hip/torso airbags, and roof rail-mounted curtain airbags. There were also second-row left and right inflatable seatbelt airbags. The driver frontal airbags (including knee bolster airbag) deployed, as did the right seat-mounted and right side curtain airbags.
+The driver sustained serious injuries and was transported by land to a nearby level-one trauma center.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1216</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>left_turn_straight</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>This case focused on the injury mechanisms of a belted 60-year-old female driver (case occupant) and a 57-year-old female right front passenger (case occupant) of a 2017 Ford Escape (V1). The collision occurred when the front of V1 collided into the front of a 2004 Jeep Liberty (V2).
+The crash occurred in the early afternoon. The roadway was a two lane undivided north/south roadway separated by a double yellow line. The roadway was in a rural area with driveways on both the east and west sides of the roadway. The roadway was straight and at the area of the collision was at a hillcrest. The roadway surface was bituminous and was dry at the time of the crash. The speed limit in the area was 89 km/h (55 mph).
+The 2017 Ford Escape (V1) was traveling south in the southbound lane of travel. The 2004 Jeep Liberty (V2) was traveling north in the northbound lane of travel. V2 was intending to make a left turn into a business parking lot. V2 crossed the double yellow line prior to beginning its left turn. V2 entered the path of V1 causing the two vehicles to collide head on in the southbound lane.
+The 60-year-old female driver (CIREN case occupant) of V1 was seated in a normal position while not using the installed lap and shoulder belt. The 57-year-old female passenger (CIREN case occupant) of V1 was seated in a normal position while using the installed lap and shoulder belt. The driver's front steering wheel hub airbag and front driver’s knee bolster airbag deployed as a result of the collision. The passenger’s upper instrument panel airbag, passenger’s seat outboard side airbag, and the passenger’s roof side rail curtain deployed as a result of the crash. Both individuals were assisted from the vehicle and transported by ground to a regional hospital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>980024</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>This crash involves a seriously injured, belted 21-year-old male driver in a 2021 Honda Accord four-door sedan that was primarily involved in a frontal impact with the front of a 2008 Toyota Avalon four-door sedan. There was also a right front female passenger in the Honda Accord.
+This crash occurred in winter on a two-way, two-lane, asphalt roadway with a concrete bridge on a rainy day. The road surface was wet from the rain. There were metal guardrails leading to the bridge for both directions of travel. The east/west roadway has a level grade in both directions. The posted speed limit was 80 km/h (50 mph) for the west lane and 72 km/h (45 mph) for the east lane.
+Vehicle 1, the 2021 Honda Accord four-door sedan, was driven by the 21-year-old male CIREN case subject in the westbound lane attempting to continue straight ahead. Vehicle 2, the 2008 Toyota Avalon four-door sedan, was traveling east in the eastbound lane attempting to continue straight ahead.
+Vehicle 2 drifted left across the center lane line. The driver in Vehicle 1 steered right and braked to avoid the collision but was unsuccessful. The front of Vehicle 2 struck the front of Vehicle 1 (Event 1). After impact, Vehicle 1 rotated counterclockwise, departed the roadway, and struck the metal guardrail with its right side (Event 2). Vehicle 1 came to rest partially off the roadway, in the shoulder and westbound travel lane facing west. Vehicle 2 rotated counterclockwise after impact and came to rest in the westbound lane facing west. Both vehicles were towed from the crash scene due to disabling damage.
+Vehicle 1 was utilizing his three-point safety belt, equipped with retractor and anchor pretensioners, and a dynamic locking latch plate. The vehicle had advanced frontal airbags (including a knee bolster), first-row seat-mounted hip/torso airbags, and roof rail-mounted curtain airbags. All airbags were deployed due to the crash. The right front passenger was also utilizing her three-point safety belt.
+The driver sustained serious injuries and was transported to a trauma center and enrolled as a CIREN case subject. The right front passenger, who is not a case subject, was transported to the trauma center by air.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>980039</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>This case focuses on the injury mechanisms of a belted 62-year-old female driver of a 2016 Volvo S60 four-door sedan (Vehicle 1), which was involved in a moderate, twelve-o’clock offset frontal impact (front left) with the frontal plane of a 2010 Toyota Corolla four-door sedan (Vehicle 2). Vehicle 1 was equipped with driver’s and passenger’s frontal airbags, seat backrest-mounted side hip/torso airbags (front outboard-seating positions), and side curtain airbags (for all outboard-seating positions).
+This two-vehicle crash occurred during the morning hours (daylight) of a winter week day, on a north/south trafficway. At the area of the crash, this north/south trafficway had two northbound lanes separated from two southbound lanes by a raised curbed median. Along the trafficway there were intermittent openings accessed by dedicated left-turn lanes, which did not play a part in the crash. The northbound travel direction had a left-turning curve with the southbound travel direction had a right-turning curve. Both bituminous roadways were level. No traffic controls were present within the crash area. At the time of the crash, the weather was clear and the roadway surfaces were dry. The posted speed limit for travel directions was 80 km/h (50mph).
+Vehicle 1, the 2016 Volvo S60 four-door sedan (case vehicle), was traveling north in the left northbound through lane, approaching the crash area from the south. The belted 62-year-old female driver (case occupant) intended to negotiate the curved section of roadway and continue traveling north. There were no other occupants within Vehicle 1.
+Vehicle 2, a 2010 Toyota Corolla four-door sedan, was traveling south, reportedly in the left southbound travel lane, approaching the crash area from the north. The driver of Vehicle 2 intended to negotiate the curved section of roadway and continue traveling south.
+For unknown reasons Vehicle 2 departed the southbound roadway to the left at the right-turning curve area of the roadway. At this time, Vehicle 2’s front wheels contacted the curbed median (events 1 and 2). Vehicle 2 traversed the median while traveling in southeasterly direction, avoiding two trees in the process. Vehicle 2 entered the northbound roadway as Vehicle 1 approached from the south. At this time, the frontal plane of Vehicle 2 struck the frontal plane of Vehicle 1 in an offset fashion (event 3). As result of this impact (event 3), Vehicle 1 rotated counterclockwise and came to rest, near the impact area, in the right northbound travel lane, facing south. Vehicle 2 rotated counterclockwise and came to rest straddling the median, at the impact area, facing an easterly direction. As a result of the impact with Vehicle 2 (event 3), Vehicle 1’s driver’s frontal airbag deployed, as did the driver’s side hip/torso airbag, and side curtain airbag.
+Following the collision, the belted 62-year-old female driver of Vehicle 1 (case occupant) was assisted/removed from the vehicle, transported by air unit to a regional trauma center, and hospitalized with minor to moderate injuries. The driver, and sole occupant of Vehicle 2, was also transported by air unit to a regional trauma center, but the extent of his injuries and treatment, if any, are unknown. Due to damage sustained in the crash, both vehicles were towed from the scene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>980112</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>left_turn_straight</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously injured, belted 46-year-old female right front passenger of a 2023 Nissan Versa compact sedan, which was primarily involved in a frontal collision with a 1989 Chevrolet GMT-400 (full-size) pickup truck.
+This two-vehicle collision occurred in the morning dawn hours under cloudy skies on a dry blacktop roadway. The collision occurred in the T-intersection of a north-south roadway and an east-west roadway. This crash case focuses on the north-south roadway. The northbound leg had one right turn lane and one through lane, while the southbound leg had one through lane. There was no traffic control for the north-south roadway and there was no physical separation. The posted speed limit was 89 km/h (55 mph).
+A 2023 Nissan Versa compact sedan (V1) was traveling northbound and intended to proceed straight through the intersection. A 1989 Chevrolet pickup truck (V2) was traveling southbound and intended to turn left to travel eastbound. As the vehicles each entered the intersection, the front plane of V1 struck the front plane of V2 (Event 1). After impact, V1 continued its northbound trajectory before coming to final rest. After impact, V2 was rotated counterclockwise before coming to rest. The vehicles were each towed from the scene due to disabling damage.
+V1 was driven by a 20-year-old male who was not enrolled as a CIREN case occupant. The 46-year-old female right front passenger of V1 was seated in an upright position. She was restrained by the available three-point lap and shoulder belt, evidenced by loading to the belt webbing, actuated retractor pretensioner, and EDR data. The instrument panel airbag and knee bolster airbag both deployed for the right front passenger seating position. The steering wheel hub airbag, knee bolster airbag, and roof-rail mounted airbag all deployed for the driver’s seating position. The vehicle was also equipped with a roof-rail mounted airbag for the right-side seating positions as well as outboard seatback airbags for all outboard seating positions, though these were not deployed.
+This case occupant was initially transported by land to a local hospital for treatment, before later being transferred to a local trauma center for treatment where she was enrolled as a CIREN case occupant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>980113</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>vehicle_encroachment</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>This crash case involves a moderately-injured belted 24-year-old male driver of a 2016 Kia Forte hatchback, which was primarily involved in a near-side left plane collision with a 2017 Kovatch Pumper fire apparatus.
+This two-vehicle collision occurred in the evening hours under clear daylit skies on a dry blacktop roadway. The collision occurred on the eastbound portion of a controlled access roadway. There were two travel lanes and no traffic controls. The posted speed limit was 89 km/h (55 mph).
+A 2017 Kovatch Pumper fire apparatus (V2) was stationary with emergency lights activated, blocking the number two lane. A 2016 Kia Forte hatchback (V1) was traveling eastbound in the number two lane and intended to continue in this lane. V1 continued in the lane and the driver did not notice V2 stationary in the lane with enough time to avoid collision. The driver of V1 did brake and swerve right immediately prior to collision, presenting the left plane of V1 to the rear right corner of V2 in a sideswipe configuration (Event 1). After impact, V1 continued its eastbound trajectory and rotated counterclockwise before coming to rest on the southern shoulder of the roadway, facing northwest. After impact, V2 was pushed forward slightly before coming to rest partially on the northern shoulder and partially in the number two lane, facing east-northeast. V1 was towed from the scene due to disabling damage. V2 was not towed.
+The 24-year-old male driver of V1 was seated in an upright position. He was restrained by the available three-point lap and shoulder belt, evidenced by loading to the belt webbing, actuated pretensioner, and EDR data. The steering wheel airbag, roof rail-mounted airbag, and outboard seatback airbag all deployed for the driver's seating position. The vehicle was also equipped with a top instrument panel airbag, roof rail-mounted airbag, and outboard seatback airbag for the right front passenger seating position, though these were not deployed.
+This case occupant was transported by land to a local trauma center, where he was enrolled as a CIREN case occupant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>980188</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>lane_departure_opposite</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>This crash case involves a seriously injured, belted 19-year-old female right front passenger of a 2018 Honda Accord four-door sedan, which was primarily involved in a frontal collision with a 2018 Ford F-150 pickup truck.
+The two-vehicle collision occurred in the afternoon hours under clear daylit skies on a dry blacktop roadway. The north-south roadway consisted of two northbound lanes and one southbound lane with no physical separation. There was a hillcrest near the area of the collision. The posted speed limit was 89 km/h (55 mph) and there were no traffic controls.
+A 2018 Honda Accord four-door sedan (V1) was traveling northbound in the number one lane and intended to continue traveling north. A 2018 Ford F-150 pickup truck (V2) was traveling southbound and entered into the northbound travel lanes. After V2 entered into the northbound lanes, the front of V1 and the front of V2 collided (Event 1). After impact, V1 came to rest facing northwest in the number one travel lane, and V2 departed the roadway before coming to rest facing north. Also after impact, V2 became engulfed in a fire (Event 2). Each vehicle was towed from the scene due to disabling damage.
+The 19-year-old female right front passenger of V1 was seated in an upright position. She was restrained by available three-point lap and shoulder belt, evidenced by loading to the restraint webbing as well as EDR data. The vehicle was equipped with top instrument panel airbag, knee bolster airbag, outboard seat-mounted airbag, and roof rail-mounted airbag for the right front seating position, all of which deployed. The vehicle was also equipped with steering wheel airbag and knee bolster airbag for the driver’s seating position, which deployed. The available outboard seat-mounted airbag and roof-rail mounted airbag for the driver’s seating position did not deploy.
+This case occupant was transported by land to a trauma center where she was enrolled as a CIREN case occupant.
+The driver in this case was a 49-year-old restrained female who was not enrolled as a CIREN case occupant.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
